--- a/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
+++ b/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E5660E-A6EC-4BFE-9EAA-AAA055763FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533F8ADF-9C59-46F3-90BA-4B30C1B2FBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1439,132 +1439,132 @@
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1965,12 +1965,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="201" t="s">
+      <c r="B3" s="206" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="202"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
@@ -2008,49 +2008,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="209" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="204"/>
+      <c r="C8" s="209"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="204"/>
-      <c r="C10" s="204"/>
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="203" t="s">
+      <c r="A13" s="208" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="203"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="203"/>
-      <c r="B14" s="203"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="203"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="203"/>
-      <c r="B16" s="203"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B22" s="200"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="239">
+      <c r="D22" s="198">
         <v>473045</v>
       </c>
       <c r="E22" s="111" t="s">
@@ -2188,10 +2188,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="197" t="s">
+      <c r="A32" s="204" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="198"/>
+      <c r="B32" s="205"/>
       <c r="C32" s="5"/>
       <c r="D32" s="110">
         <v>174848.74</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B36" s="200"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="238">
+      <c r="D36" s="197">
         <v>75000</v>
       </c>
       <c r="E36" s="111" t="s">
@@ -2503,8 +2503,8 @@
       <c r="E60" s="73"/>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="207"/>
-      <c r="B61" s="207"/>
+      <c r="A61" s="203"/>
+      <c r="B61" s="203"/>
       <c r="C61" s="5"/>
       <c r="D61" s="110"/>
       <c r="E61" s="73"/>
@@ -2727,16 +2727,16 @@
     </row>
     <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="206" t="s">
+      <c r="A94" s="202" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="206"/>
-      <c r="C94" s="206"/>
+      <c r="B94" s="202"/>
+      <c r="C94" s="202"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="206"/>
-      <c r="B95" s="206"/>
-      <c r="C95" s="206"/>
+      <c r="A95" s="202"/>
+      <c r="B95" s="202"/>
+      <c r="C95" s="202"/>
     </row>
     <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="87"/>
@@ -2766,35 +2766,42 @@
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="205"/>
-      <c r="B100" s="205"/>
-      <c r="C100" s="205"/>
-      <c r="D100" s="205"/>
-      <c r="E100" s="205"/>
+      <c r="A100" s="201"/>
+      <c r="B100" s="201"/>
+      <c r="C100" s="201"/>
+      <c r="D100" s="201"/>
+      <c r="E100" s="201"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="205"/>
-      <c r="B101" s="205"/>
-      <c r="C101" s="205"/>
-      <c r="D101" s="205"/>
-      <c r="E101" s="205"/>
+      <c r="A101" s="201"/>
+      <c r="B101" s="201"/>
+      <c r="C101" s="201"/>
+      <c r="D101" s="201"/>
+      <c r="E101" s="201"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="205"/>
-      <c r="B102" s="205"/>
-      <c r="C102" s="205"/>
-      <c r="D102" s="205"/>
-      <c r="E102" s="205"/>
+      <c r="A102" s="201"/>
+      <c r="B102" s="201"/>
+      <c r="C102" s="201"/>
+      <c r="D102" s="201"/>
+      <c r="E102" s="201"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="205"/>
-      <c r="B103" s="205"/>
-      <c r="C103" s="205"/>
-      <c r="D103" s="205"/>
-      <c r="E103" s="205"/>
+      <c r="A103" s="201"/>
+      <c r="B103" s="201"/>
+      <c r="C103" s="201"/>
+      <c r="D103" s="201"/>
+      <c r="E103" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="A94:C95"/>
@@ -2802,13 +2809,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2844,15 +2844,15 @@
       <c r="B1" s="148"/>
       <c r="C1" s="149"/>
       <c r="D1" s="149"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
       <c r="N1" s="148"/>
       <c r="O1" s="150"/>
     </row>
@@ -2901,198 +2901,198 @@
       <c r="P3" s="20"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="222" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="221"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="224"/>
       <c r="P4" s="20"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="223"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="223"/>
-      <c r="O5" s="224"/>
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="227"/>
       <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="222"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="223"/>
-      <c r="O6" s="224"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="227"/>
       <c r="P6" s="20"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="224"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="227"/>
       <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="225"/>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="226"/>
-      <c r="O8" s="227"/>
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="230"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="230" t="s">
+      <c r="A9" s="233" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="231"/>
-      <c r="H9" s="231"/>
-      <c r="I9" s="231"/>
-      <c r="J9" s="231"/>
-      <c r="K9" s="231"/>
-      <c r="L9" s="231"/>
-      <c r="M9" s="231"/>
-      <c r="N9" s="231"/>
-      <c r="O9" s="231"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="232" t="s">
+      <c r="A10" s="235" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="232"/>
-      <c r="C10" s="232"/>
-      <c r="D10" s="232"/>
-      <c r="E10" s="232"/>
-      <c r="F10" s="232"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="232"/>
-      <c r="I10" s="232"/>
-      <c r="J10" s="232"/>
-      <c r="K10" s="232"/>
-      <c r="L10" s="232"/>
-      <c r="M10" s="232"/>
-      <c r="N10" s="232"/>
-      <c r="O10" s="232"/>
+      <c r="B10" s="235"/>
+      <c r="C10" s="235"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
+      <c r="N10" s="235"/>
+      <c r="O10" s="235"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="213" t="s">
+      <c r="A11" s="210" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="123"/>
-      <c r="C11" s="213" t="s">
+      <c r="C11" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="213" t="s">
+      <c r="D11" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="213" t="s">
+      <c r="E11" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="209" t="s">
+      <c r="F11" s="214" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="213" t="s">
+      <c r="G11" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="215" t="s">
+      <c r="H11" s="218" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="209" t="s">
+      <c r="I11" s="214" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="209" t="s">
+      <c r="J11" s="214" t="s">
         <v>95</v>
       </c>
-      <c r="K11" s="217" t="s">
+      <c r="K11" s="220" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="209" t="s">
+      <c r="L11" s="214" t="s">
         <v>80</v>
       </c>
       <c r="M11" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="211" t="s">
+      <c r="N11" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="228" t="s">
+      <c r="O11" s="231" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="214"/>
+      <c r="A12" s="212"/>
       <c r="B12" s="124"/>
-      <c r="C12" s="214"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="214"/>
-      <c r="F12" s="210"/>
-      <c r="G12" s="214"/>
-      <c r="H12" s="216"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="210"/>
-      <c r="K12" s="218"/>
-      <c r="L12" s="210"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="215"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="215"/>
+      <c r="J12" s="215"/>
+      <c r="K12" s="221"/>
+      <c r="L12" s="215"/>
       <c r="M12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="212"/>
-      <c r="O12" s="229"/>
+      <c r="N12" s="217"/>
+      <c r="O12" s="232"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
@@ -3189,19 +3189,19 @@
       </c>
       <c r="L14" s="189">
         <f>EDESUR!I6</f>
-        <v>24102.857781768264</v>
+        <v>32287.37</v>
       </c>
       <c r="M14" s="187">
         <f t="shared" si="3"/>
-        <v>164469.01999999999</v>
+        <v>172653.02</v>
       </c>
       <c r="N14" s="59">
         <f t="shared" ref="N14:N30" si="5">ROUND(M14*6% + M14,0) + P14</f>
-        <v>174337.02</v>
+        <v>183012.02</v>
       </c>
       <c r="O14" s="60">
         <f t="shared" ref="O14:O35" si="6">ROUND(M14*3%,0) + M14</f>
-        <v>169403.02</v>
+        <v>177833.02</v>
       </c>
       <c r="P14" s="31">
         <f>P13+0.01</f>
@@ -3249,19 +3249,19 @@
       </c>
       <c r="L15" s="189">
         <f>EDESUR!I7</f>
-        <v>20750.545398450711</v>
+        <v>37878.74</v>
       </c>
       <c r="M15" s="187">
         <f t="shared" si="3"/>
-        <v>139551.03</v>
+        <v>156679.03</v>
       </c>
       <c r="N15" s="59">
         <f t="shared" si="5"/>
-        <v>147924.03</v>
+        <v>166080.03</v>
       </c>
       <c r="O15" s="60">
         <f t="shared" si="6"/>
-        <v>143738.03</v>
+        <v>161379.03</v>
       </c>
       <c r="P15" s="31">
         <f t="shared" ref="P15:P30" si="7">P14+0.01</f>
@@ -3549,19 +3549,19 @@
       </c>
       <c r="L20" s="189">
         <f>EDESUR!I13</f>
-        <v>43777.036573498022</v>
+        <v>93523.69</v>
       </c>
       <c r="M20" s="187">
         <f t="shared" si="3"/>
-        <v>188977.08</v>
+        <v>238724.08</v>
       </c>
       <c r="N20" s="184">
         <f t="shared" si="5"/>
-        <v>200316.08</v>
+        <v>253048.08</v>
       </c>
       <c r="O20" s="185">
         <f t="shared" si="6"/>
-        <v>194646.08</v>
+        <v>245886.07999999999</v>
       </c>
       <c r="P20" s="31">
         <f t="shared" si="7"/>
@@ -4476,15 +4476,15 @@
       <c r="L36" s="186"/>
       <c r="M36" s="68">
         <f>SUM(M13:M35)</f>
-        <v>2422123.7600000012</v>
+        <v>2497182.7600000012</v>
       </c>
       <c r="N36" s="68">
         <f t="shared" si="11"/>
-        <v>2518477.7100000009</v>
+        <v>2598040.7100000009</v>
       </c>
       <c r="O36" s="68">
         <f>SUM(O13:O35)</f>
-        <v>2494788.7600000012</v>
+        <v>2572099.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4493,93 +4493,88 @@
     </row>
     <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="205" t="str">
+      <c r="C39" s="201" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="205"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="205"/>
-      <c r="H39" s="205"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-      <c r="M39" s="205"/>
+      <c r="D39" s="201"/>
+      <c r="E39" s="201"/>
+      <c r="F39" s="201"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="201"/>
+      <c r="I39" s="201"/>
+      <c r="J39" s="201"/>
+      <c r="K39" s="201"/>
+      <c r="L39" s="201"/>
+      <c r="M39" s="201"/>
     </row>
     <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="205"/>
-      <c r="D40" s="205"/>
-      <c r="E40" s="205"/>
-      <c r="F40" s="205"/>
-      <c r="G40" s="205"/>
-      <c r="H40" s="205"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="205"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="205"/>
-      <c r="M40" s="205"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="201"/>
+      <c r="F40" s="201"/>
+      <c r="G40" s="201"/>
+      <c r="H40" s="201"/>
+      <c r="I40" s="201"/>
+      <c r="J40" s="201"/>
+      <c r="K40" s="201"/>
+      <c r="L40" s="201"/>
+      <c r="M40" s="201"/>
     </row>
     <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="205"/>
-      <c r="D41" s="205"/>
-      <c r="E41" s="205"/>
-      <c r="F41" s="205"/>
-      <c r="G41" s="205"/>
-      <c r="H41" s="205"/>
-      <c r="I41" s="205"/>
-      <c r="J41" s="205"/>
-      <c r="K41" s="205"/>
-      <c r="L41" s="205"/>
-      <c r="M41" s="205"/>
+      <c r="C41" s="201"/>
+      <c r="D41" s="201"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="201"/>
+      <c r="G41" s="201"/>
+      <c r="H41" s="201"/>
+      <c r="I41" s="201"/>
+      <c r="J41" s="201"/>
+      <c r="K41" s="201"/>
+      <c r="L41" s="201"/>
+      <c r="M41" s="201"/>
     </row>
     <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="205"/>
-      <c r="D42" s="205"/>
-      <c r="E42" s="205"/>
-      <c r="F42" s="205"/>
-      <c r="G42" s="205"/>
-      <c r="H42" s="205"/>
-      <c r="I42" s="205"/>
-      <c r="J42" s="205"/>
-      <c r="K42" s="205"/>
-      <c r="L42" s="205"/>
-      <c r="M42" s="205"/>
+      <c r="C42" s="201"/>
+      <c r="D42" s="201"/>
+      <c r="E42" s="201"/>
+      <c r="F42" s="201"/>
+      <c r="G42" s="201"/>
+      <c r="H42" s="201"/>
+      <c r="I42" s="201"/>
+      <c r="J42" s="201"/>
+      <c r="K42" s="201"/>
+      <c r="L42" s="201"/>
+      <c r="M42" s="201"/>
     </row>
     <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="205"/>
-      <c r="D43" s="205"/>
-      <c r="E43" s="205"/>
-      <c r="F43" s="205"/>
-      <c r="G43" s="205"/>
-      <c r="H43" s="205"/>
-      <c r="I43" s="205"/>
-      <c r="J43" s="205"/>
-      <c r="K43" s="205"/>
-      <c r="L43" s="205"/>
-      <c r="M43" s="205"/>
+      <c r="C43" s="201"/>
+      <c r="D43" s="201"/>
+      <c r="E43" s="201"/>
+      <c r="F43" s="201"/>
+      <c r="G43" s="201"/>
+      <c r="H43" s="201"/>
+      <c r="I43" s="201"/>
+      <c r="J43" s="201"/>
+      <c r="K43" s="201"/>
+      <c r="L43" s="201"/>
+      <c r="M43" s="201"/>
     </row>
     <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="205"/>
-      <c r="D44" s="205"/>
-      <c r="E44" s="205"/>
-      <c r="F44" s="205"/>
-      <c r="G44" s="205"/>
-      <c r="H44" s="205"/>
-      <c r="I44" s="205"/>
-      <c r="J44" s="205"/>
-      <c r="K44" s="205"/>
-      <c r="L44" s="205"/>
-      <c r="M44" s="205"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="201"/>
+      <c r="G44" s="201"/>
+      <c r="H44" s="201"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="201"/>
+      <c r="L44" s="201"/>
+      <c r="M44" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C39:M44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4593,6 +4588,11 @@
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A10:O10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4625,18 +4625,18 @@
       <c r="G3" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="I3" s="236" t="s">
+      <c r="I3" s="238" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="237"/>
+      <c r="J3" s="239"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="134"/>
       <c r="C4" s="134"/>
       <c r="E4" s="134"/>
       <c r="G4" s="137"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="237"/>
+      <c r="I4" s="238"/>
+      <c r="J4" s="239"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="134">
@@ -4646,17 +4646,18 @@
         <v>83</v>
       </c>
       <c r="E5" s="138">
-        <v>4843.2564768292677</v>
+        <v>4778.67</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="139">
-        <v>4843.2564768292677</v>
-      </c>
-      <c r="I5" s="234">
+        <f>E5</f>
+        <v>4778.67</v>
+      </c>
+      <c r="I5" s="236">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="235"/>
+      <c r="J5" s="237"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="134">
@@ -4666,17 +4667,17 @@
         <v>84</v>
       </c>
       <c r="E6" s="138">
-        <v>24102.857781768264</v>
+        <v>32287.37</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="139">
         <v>0</v>
       </c>
-      <c r="I6" s="234">
+      <c r="I6" s="236">
         <f t="shared" ref="I6:I21" si="0">E6-G6</f>
-        <v>24102.857781768264</v>
-      </c>
-      <c r="J6" s="235"/>
+        <v>32287.37</v>
+      </c>
+      <c r="J6" s="237"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="134">
@@ -4686,17 +4687,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="138">
-        <v>30937.92295115858</v>
+        <v>37878.74</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="139">
-        <v>10187.377552707869</v>
-      </c>
-      <c r="I7" s="234">
+      <c r="G7" s="139"/>
+      <c r="I7" s="236">
         <f t="shared" si="0"/>
-        <v>20750.545398450711</v>
-      </c>
-      <c r="J7" s="235"/>
+        <v>37878.74</v>
+      </c>
+      <c r="J7" s="237"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="134">
@@ -4706,17 +4705,18 @@
         <v>83</v>
       </c>
       <c r="E8" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I8" s="234">
+        <f>E8</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I8" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="235"/>
+      <c r="J8" s="237"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="135">
@@ -4726,17 +4726,18 @@
         <v>86</v>
       </c>
       <c r="E9" s="138">
-        <v>2663.7910622560971</v>
+        <v>2628.27</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="139">
-        <v>2663.7910622560971</v>
-      </c>
-      <c r="I9" s="234">
+        <f>E9</f>
+        <v>2628.27</v>
+      </c>
+      <c r="I9" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="235"/>
+      <c r="J9" s="237"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="135">
@@ -4746,17 +4747,18 @@
         <v>84</v>
       </c>
       <c r="E10" s="138">
-        <v>2663.7910622560971</v>
+        <v>2628.27</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="139">
-        <v>2663.7910622560971</v>
-      </c>
-      <c r="I10" s="234">
+        <f>E10</f>
+        <v>2628.27</v>
+      </c>
+      <c r="I10" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="235"/>
+      <c r="J10" s="237"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="135">
@@ -4766,17 +4768,18 @@
         <v>85</v>
       </c>
       <c r="E11" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I11" s="234">
+        <f>E11</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I11" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="235"/>
+      <c r="J11" s="237"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="135">
@@ -4786,17 +4789,18 @@
         <v>83</v>
       </c>
       <c r="E12" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I12" s="234">
+        <f>E12</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I12" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="235"/>
+      <c r="J12" s="237"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="134">
@@ -4806,17 +4810,15 @@
         <v>86</v>
       </c>
       <c r="E13" s="138">
-        <v>82372.476165914617</v>
+        <v>93523.69</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="139">
-        <v>38595.439592416595</v>
-      </c>
-      <c r="I13" s="234">
+      <c r="G13" s="139"/>
+      <c r="I13" s="236">
         <f t="shared" si="0"/>
-        <v>43777.036573498022</v>
-      </c>
-      <c r="J13" s="235"/>
+        <v>93523.69</v>
+      </c>
+      <c r="J13" s="237"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="135">
@@ -4826,17 +4828,18 @@
         <v>84</v>
       </c>
       <c r="E14" s="138">
-        <v>2663.7910622560971</v>
+        <v>2628.27</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="139">
-        <v>2663.7910622560971</v>
-      </c>
-      <c r="I14" s="234">
+        <f>E14</f>
+        <v>2628.27</v>
+      </c>
+      <c r="I14" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="235"/>
+      <c r="J14" s="237"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="135">
@@ -4846,17 +4849,18 @@
         <v>85</v>
       </c>
       <c r="E15" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I15" s="234">
+        <f>E15</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I15" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="235"/>
+      <c r="J15" s="237"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="134">
@@ -4866,17 +4870,18 @@
         <v>83</v>
       </c>
       <c r="E16" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I16" s="234">
+        <f>E16</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I16" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="235"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="135">
@@ -4886,17 +4891,18 @@
         <v>86</v>
       </c>
       <c r="E17" s="138">
-        <v>2663.7910622560971</v>
+        <v>2628.27</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="139">
-        <v>2663.7910622560971</v>
-      </c>
-      <c r="I17" s="234">
+        <f>E17</f>
+        <v>2628.27</v>
+      </c>
+      <c r="I17" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="235"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="134">
@@ -4906,17 +4912,18 @@
         <v>84</v>
       </c>
       <c r="E18" s="138">
-        <v>2663.7910622560971</v>
+        <v>2628.27</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="139">
-        <v>2663.7910622560971</v>
-      </c>
-      <c r="I18" s="234">
+        <f>E18</f>
+        <v>2628.27</v>
+      </c>
+      <c r="I18" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="235"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="135">
@@ -4926,25 +4933,26 @@
         <v>85</v>
       </c>
       <c r="E19" s="138">
-        <v>2179.4654145731706</v>
+        <v>2150.4</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="139">
-        <v>2179.4654145731706</v>
-      </c>
-      <c r="I19" s="234">
+        <f>E19</f>
+        <v>2150.4</v>
+      </c>
+      <c r="I19" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="235"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="134"/>
       <c r="C20" s="134"/>
       <c r="E20" s="134"/>
       <c r="G20" s="137"/>
-      <c r="I20" s="234"/>
-      <c r="J20" s="235"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="237"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="168" t="s">
@@ -4954,18 +4962,18 @@
       <c r="D21" s="169"/>
       <c r="E21" s="170">
         <f>SUM(E5:E20)</f>
-        <v>168652.26117439024</v>
+        <v>194512.21999999994</v>
       </c>
       <c r="F21" s="171"/>
       <c r="G21" s="170">
         <f>SUM(G5:G20)</f>
-        <v>80021.821420673266</v>
-      </c>
-      <c r="I21" s="234">
-        <f t="shared" si="0"/>
-        <v>88630.439753716972</v>
-      </c>
-      <c r="J21" s="235"/>
+        <v>30822.420000000006</v>
+      </c>
+      <c r="I21" s="236">
+        <f>E21-G21</f>
+        <v>163689.79999999993</v>
+      </c>
+      <c r="J21" s="237"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="134" t="s">
@@ -4975,17 +4983,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="144">
-        <v>282.5232944817073</v>
+        <v>278.76</v>
       </c>
       <c r="G22" s="145">
         <f>E22</f>
-        <v>282.5232944817073</v>
-      </c>
-      <c r="I22" s="234">
+        <v>278.76</v>
+      </c>
+      <c r="I22" s="236">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="235"/>
+      <c r="J22" s="237"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="134" t="s">
@@ -4995,17 +5003,17 @@
         <v>2</v>
       </c>
       <c r="E23" s="144">
-        <v>242.16282384146339</v>
+        <v>238.93</v>
       </c>
       <c r="G23" s="145">
         <f t="shared" ref="G23:G29" si="2">E23</f>
-        <v>242.16282384146339</v>
-      </c>
-      <c r="I23" s="234">
+        <v>238.93</v>
+      </c>
+      <c r="I23" s="236">
         <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="235"/>
+      <c r="J23" s="237"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="134" t="s">
@@ -5015,17 +5023,17 @@
         <v>3</v>
       </c>
       <c r="E24" s="144">
-        <v>242.16282384146339</v>
+        <v>238.93</v>
       </c>
       <c r="G24" s="145">
         <f t="shared" si="2"/>
-        <v>242.16282384146339</v>
-      </c>
-      <c r="I24" s="234">
+        <v>238.93</v>
+      </c>
+      <c r="I24" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="235"/>
+      <c r="J24" s="237"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="134" t="s">
@@ -5035,17 +5043,17 @@
         <v>4</v>
       </c>
       <c r="E25" s="144">
-        <v>242.16282384146339</v>
+        <v>238.93</v>
       </c>
       <c r="G25" s="145">
         <f t="shared" si="2"/>
-        <v>242.16282384146339</v>
-      </c>
-      <c r="I25" s="234">
+        <v>238.93</v>
+      </c>
+      <c r="I25" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="235"/>
+      <c r="J25" s="237"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="134" t="s">
@@ -5055,17 +5063,17 @@
         <v>5</v>
       </c>
       <c r="E26" s="144">
-        <v>242.16282384146339</v>
+        <v>238.93</v>
       </c>
       <c r="G26" s="145">
         <f t="shared" si="2"/>
-        <v>242.16282384146339</v>
-      </c>
-      <c r="I26" s="234">
+        <v>238.93</v>
+      </c>
+      <c r="I26" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="235"/>
+      <c r="J26" s="237"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="134" t="s">
@@ -5075,17 +5083,17 @@
         <v>6</v>
       </c>
       <c r="E27" s="144">
-        <v>121.0814119207317</v>
+        <v>119.47</v>
       </c>
       <c r="G27" s="145">
         <f t="shared" si="2"/>
-        <v>121.0814119207317</v>
-      </c>
-      <c r="I27" s="234">
+        <v>119.47</v>
+      </c>
+      <c r="I27" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="235"/>
+      <c r="J27" s="237"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="134" t="s">
@@ -5095,17 +5103,17 @@
         <v>7</v>
       </c>
       <c r="E28" s="144">
-        <v>121.0814119207317</v>
+        <v>119.47</v>
       </c>
       <c r="G28" s="145">
         <f t="shared" si="2"/>
-        <v>121.0814119207317</v>
-      </c>
-      <c r="I28" s="234">
+        <v>119.47</v>
+      </c>
+      <c r="I28" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="235"/>
+      <c r="J28" s="237"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="134" t="s">
@@ -5115,17 +5123,17 @@
         <v>8</v>
       </c>
       <c r="E29" s="144">
-        <v>121.0814119207317</v>
+        <v>119.47</v>
       </c>
       <c r="G29" s="145">
         <f t="shared" si="2"/>
-        <v>121.0814119207317</v>
-      </c>
-      <c r="I29" s="234">
+        <v>119.47</v>
+      </c>
+      <c r="I29" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="235"/>
+      <c r="J29" s="237"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="173" t="s">
@@ -5135,66 +5143,51 @@
       <c r="D30" s="172"/>
       <c r="E30" s="170">
         <f>SUM(E22:E29)</f>
-        <v>1614.4188256097557</v>
+        <v>1592.8900000000003</v>
       </c>
       <c r="F30" s="172"/>
       <c r="G30" s="170">
         <f>SUM(G22:G29)</f>
-        <v>1614.4188256097557</v>
-      </c>
-      <c r="I30" s="234">
+        <v>1592.8900000000003</v>
+      </c>
+      <c r="I30" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="235"/>
+      <c r="J30" s="237"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="142"/>
       <c r="G31" s="139"/>
-      <c r="I31" s="234">
+      <c r="I31" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="235"/>
+      <c r="J31" s="237"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="140"/>
       <c r="G32" s="141"/>
-      <c r="I32" s="234"/>
-      <c r="J32" s="235"/>
+      <c r="I32" s="236"/>
+      <c r="J32" s="237"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="142">
         <f>E30+E21</f>
-        <v>170266.68</v>
+        <v>196105.10999999996</v>
       </c>
       <c r="G33" s="139">
         <f>G21+G30</f>
-        <v>81636.240246283021</v>
-      </c>
-      <c r="I33" s="234">
+        <v>32415.310000000005</v>
+      </c>
+      <c r="I33" s="236">
         <f>E33-G33</f>
-        <v>88630.439753716972</v>
-      </c>
-      <c r="J33" s="235"/>
+        <v>163689.79999999996</v>
+      </c>
+      <c r="J33" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5211,6 +5204,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
+++ b/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533F8ADF-9C59-46F3-90BA-4B30C1B2FBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747566AE-820F-4B08-81FD-394621C17F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,19 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="143">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -398,9 +403,6 @@
   </si>
   <si>
     <t>Bonificado x EDESUR Noviembre</t>
-  </si>
-  <si>
-    <t>Sr. Hector Piletero</t>
   </si>
   <si>
     <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
@@ -423,48 +425,9 @@
     <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
-    <t>Transf 04/02</t>
-  </si>
-  <si>
-    <t>Debito 06/02</t>
-  </si>
-  <si>
-    <t>Transf 20/02</t>
-  </si>
-  <si>
-    <t>Compra de pilas para SUM</t>
-  </si>
-  <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
-    <t>Sagitario - compra de pintura arreglos interiores de departamentos</t>
-  </si>
-  <si>
-    <t>Transf 23/02</t>
-  </si>
-  <si>
-    <t>Kromacolor - Compra de pintura cielo raso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emergencia secado de rotura de termotanque : Sra. Silvana </t>
-  </si>
-  <si>
-    <t>Sr. Felix 3D</t>
-  </si>
-  <si>
-    <t>Sr. Gabriel Pintor - Mano de obra dpto. 4D y 3D (Humedades traspasadas por terrazas y medianeras)</t>
-  </si>
-  <si>
-    <t>Transf 27/02</t>
-  </si>
-  <si>
     <t>Cristian Rodrigo Centurion</t>
   </si>
   <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 1  - Restan 6 cuotas de $157.988,29</t>
-  </si>
-  <si>
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE SALTA 1167</t>
   </si>
   <si>
@@ -475,6 +438,33 @@
   </si>
   <si>
     <t>Transf 03/03</t>
+  </si>
+  <si>
+    <t>Transf 04/03</t>
+  </si>
+  <si>
+    <t>Debito 06/03</t>
+  </si>
+  <si>
+    <t>Sr. Herrero - Arreglo porton - Diego Martin Giuffre</t>
+  </si>
+  <si>
+    <t>Transf 16/03</t>
+  </si>
+  <si>
+    <t>No se transfeiere</t>
+  </si>
+  <si>
+    <t>Compra de pilas - SUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efectivo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocacion termo </t>
+  </si>
+  <si>
+    <t>Easy Barracas - Compra de termotanque - Cuota 1  - Restan 5 cuotas de $157.988,29</t>
   </si>
 </sst>
 </file>
@@ -493,7 +483,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,6 +677,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1117,7 +1116,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1151,7 +1150,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1264,12 +1262,7 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,13 +1304,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1430,18 +1418,34 @@
     <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1644,9 +1648,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1684,9 +1688,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1719,9 +1723,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1754,9 +1775,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1930,134 +1968,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M100"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="54"/>
-    </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="207" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="207"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="208"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C5" s="15"/>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="209" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="209"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="208" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="210" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="210"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="210"/>
+      <c r="C9" s="210"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="210"/>
+      <c r="C10" s="210"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="208"/>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="208"/>
-      <c r="B15" s="208"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="208"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="209"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>105</v>
       </c>
@@ -2066,732 +2104,685 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>78</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="101"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="199" t="s">
+      <c r="D21" s="109"/>
+      <c r="E21" s="100"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="200" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="200"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="198">
+      <c r="B22" s="201"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="110">
         <v>473045</v>
       </c>
-      <c r="E22" s="111" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="90"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="199"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="109"/>
-      <c r="H23" s="90"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="105" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" s="89"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="200"/>
+      <c r="B23" s="201"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="103"/>
+      <c r="H23" s="89"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="130">
+      <c r="D24" s="111"/>
+      <c r="E24" s="189">
         <f>SUM(D22:D23)</f>
         <v>473045</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="129"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="199" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="200"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="177">
-        <v>74584</v>
-      </c>
-      <c r="E26" s="196" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D25" s="112"/>
+      <c r="E25" s="190"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="200" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="201"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="168">
+        <v>75267</v>
+      </c>
+      <c r="E26" s="186" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="102">
+      <c r="D27" s="111"/>
+      <c r="E27" s="123">
         <f>SUM(D26:D26)</f>
-        <v>74584</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>75267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="105"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="191"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="109"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="104"/>
+      <c r="E29" s="103"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="110">
-        <v>5432.38</v>
-      </c>
-      <c r="E30" s="109" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D30" s="104">
+        <v>6040.73</v>
+      </c>
+      <c r="E30" s="103" t="str">
+        <f>E31</f>
+        <v>Transf 04/03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="126"/>
+      <c r="B31" s="120"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="110">
-        <v>275382.28999999998</v>
-      </c>
-      <c r="E31" s="109" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="204" t="s">
+      <c r="D31" s="104">
+        <v>247384</v>
+      </c>
+      <c r="E31" s="103" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="205" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="205"/>
+      <c r="B32" s="206"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="110">
+      <c r="D32" s="104">
         <v>174848.74</v>
       </c>
-      <c r="E32" s="109" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="112" t="s">
+      <c r="E32" s="103" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="108"/>
+      <c r="B33" s="102"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="110">
-        <v>22064.59</v>
-      </c>
-      <c r="E33" s="109" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="104">
+        <v>23057.47</v>
+      </c>
+      <c r="E33" s="103" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="103">
+      <c r="D34" s="114"/>
+      <c r="E34" s="192">
         <f>SUM(D29:D33)</f>
-        <v>477728</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>451330.93999999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="106"/>
-    </row>
-    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="199" t="s">
+      <c r="D35" s="111"/>
+      <c r="E35" s="193"/>
+    </row>
+    <row r="36" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="200" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="200"/>
+      <c r="B36" s="201"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="197">
+      <c r="D36" s="104">
         <v>75000</v>
       </c>
-      <c r="E36" s="111" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="127" t="s">
+      <c r="E36" s="105" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="128"/>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="187" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="188"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="75">
+      <c r="D37" s="74">
         <v>4800</v>
       </c>
-      <c r="E37" s="111" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="192" t="s">
+      <c r="E37" s="105" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="198" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="199"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="74">
+        <v>60000</v>
+      </c>
+      <c r="E38" s="105" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="200" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="201"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="74">
+        <v>157988.29</v>
+      </c>
+      <c r="E39" s="105"/>
+    </row>
+    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="200" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="201"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="74">
+        <v>50000</v>
+      </c>
+      <c r="E40" s="105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="123">
+        <f>SUM(D36:D40)</f>
+        <v>347788.29000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="194"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="200" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="201"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="75">
-        <v>24000</v>
-      </c>
-      <c r="E38" s="111" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="127" t="s">
-        <v>137</v>
-      </c>
-      <c r="B39" s="128"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="75">
-        <v>16986.78</v>
-      </c>
-      <c r="E39" s="111" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="192" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="128"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="75">
-        <v>42385.55</v>
-      </c>
-      <c r="E40" s="111" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" s="193"/>
-    </row>
-    <row r="41" spans="1:7" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="199" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" s="200"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="75">
-        <v>56875.79</v>
-      </c>
-      <c r="E41" s="111" t="s">
-        <v>139</v>
-      </c>
-      <c r="F41" s="193"/>
-      <c r="G41" s="193"/>
-    </row>
-    <row r="42" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="199" t="s">
-        <v>140</v>
-      </c>
-      <c r="B42" s="200"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="75">
-        <v>320000</v>
-      </c>
-      <c r="E42" s="111" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-    </row>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B43" s="128"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="116">
-        <v>74600</v>
-      </c>
-      <c r="E43" s="111" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="102">
-        <f>SUM(D36:D43)</f>
-        <v>614648.12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="115"/>
-      <c r="E45" s="101"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="199" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="200"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="116">
-        <v>150000</v>
-      </c>
-      <c r="E46" s="133" t="s">
-        <v>141</v>
-      </c>
-      <c r="G46" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="127"/>
-      <c r="B47" s="128"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="143"/>
-      <c r="E47" s="133"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="s">
+      <c r="E43" s="195"/>
+      <c r="G43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="121"/>
+      <c r="B44" s="122"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="134"/>
+      <c r="E44" s="195"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="130">
-        <f>SUM(D46:D47)</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="25" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="189">
+        <f>SUM(D43:D44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="49"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="114"/>
-      <c r="E49" s="102"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="B46" s="48"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="123"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="196"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="104">
+        <v>27165.99</v>
+      </c>
+      <c r="E48" s="197"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="123">
+        <f>SUM(D47:D48)</f>
+        <v>27165.99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="110"/>
-      <c r="E50" s="107"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="110">
-        <v>21963.1</v>
-      </c>
-      <c r="E51" s="29"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="131">
-        <f>SUM(D50:D51)</f>
-        <v>21963.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="78"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="22" t="s">
+      <c r="D50" s="71"/>
+      <c r="E50" s="77"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="124">
+        <f>(2200000)-1314557.42-60000-39.8</f>
+        <v>825402.78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="30"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="8"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="82">
+        <f>(SUM(E21:E51))</f>
+        <v>2200000</v>
+      </c>
+      <c r="F53" s="99"/>
+      <c r="G53" s="30"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D54" s="79"/>
-      <c r="E54" s="132">
-        <f>2200000-1811968.22</f>
-        <v>388031.78</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="31"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="83">
-        <f>(SUM(E21:E54))</f>
+      <c r="E54" s="79"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D55" s="79"/>
+      <c r="E55" s="79"/>
+      <c r="H55" s="115"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" s="10"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="84"/>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="73"/>
+      <c r="B57" s="102"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="72"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="204"/>
+      <c r="B58" s="204"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="72"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="73"/>
+      <c r="B60" s="75"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="72"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="35"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41">
+        <f>SUM(D57:D60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="182"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="8"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="49">
+        <f>E61+E64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="B68" s="70">
+        <f>E53</f>
         <v>2200000</v>
       </c>
-      <c r="F56" s="100"/>
-      <c r="G56" s="31"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-    </row>
-    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="H58" s="121"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="84"/>
-      <c r="E59" s="85"/>
-    </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="74"/>
-      <c r="B60" s="108"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="73"/>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="203"/>
-      <c r="B61" s="203"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="110"/>
-      <c r="E61" s="73"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="74"/>
-      <c r="B63" s="76"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="75"/>
-      <c r="E63" s="73"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42">
-        <f>SUM(D60:D63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="191"/>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="50">
-        <f>E64+E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="B71" s="71">
-        <f>E56</f>
-        <v>2200000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="70" t="s">
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="71">
-        <f>E56-E54</f>
-        <v>1811968.22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="70" t="s">
+      <c r="B69" s="70">
+        <f>E53-E51</f>
+        <v>1374597.22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="71">
-        <f>E69-E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="70" t="s">
+      <c r="B70" s="70">
+        <f>E66-E64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="71">
-        <f>E69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="27"/>
-    </row>
-    <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="92" t="s">
+      <c r="B71" s="70">
+        <f>E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="27"/>
+    </row>
+    <row r="74" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="146">
-        <v>-672526.10000000033</v>
-      </c>
-      <c r="C77" s="27"/>
-      <c r="D77" s="34"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="41" t="s">
+      <c r="B74" s="137">
+        <v>-481117.02000000095</v>
+      </c>
+      <c r="C74" s="27"/>
+      <c r="D74" s="33"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B78" s="97">
-        <f>-B72</f>
-        <v>-1811968.22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="41" t="s">
+      <c r="B75" s="96">
+        <f>-B69</f>
+        <v>-1374597.22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B79" s="97">
-        <f>B98</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="41" t="s">
+      <c r="B76" s="96">
+        <f>B95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="98">
-        <f>PRORRATEO!G36-B88</f>
-        <v>2003377.2999999993</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="B81" s="98"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="99" t="s">
+      <c r="B77" s="97">
+        <f>PRORRATEO!G36-B85</f>
+        <v>2275561.9000000008</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="97"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="122"/>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="95" t="s">
+      <c r="B79" s="116"/>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="94" t="s">
         <v>114</v>
       </c>
+      <c r="B80" s="95">
+        <f>SUM(B74:C79)</f>
+        <v>419847.65999999992</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="92"/>
+      <c r="B81" s="92"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="29"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" s="137">
+        <v>2000000</v>
+      </c>
+      <c r="D82" s="29"/>
+      <c r="E82" s="30"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="B83" s="96">
-        <f>SUM(B77:C82)</f>
-        <v>-481117.02000000095</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="93"/>
-      <c r="B84" s="93"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="30"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="B85" s="146">
+        <f>-B70</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="30"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" s="96">
+        <f>B103</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="30"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" s="97">
+        <v>0</v>
+      </c>
+      <c r="D85" s="183"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="98" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" s="116"/>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="B87" s="95">
+        <f>SUM(B82:C86)</f>
         <v>2000000</v>
       </c>
-      <c r="D85" s="30"/>
-      <c r="E85" s="31"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B86" s="97">
-        <f>-B73</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="31"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B87" s="97">
-        <f>B106</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="31"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B88" s="98">
-        <v>0</v>
-      </c>
-      <c r="D88" s="193"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="99" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" s="122"/>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="95" t="s">
-        <v>115</v>
-      </c>
-      <c r="B90" s="96">
-        <f>SUM(B85:C89)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="93"/>
-      <c r="B91" s="93"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="93"/>
-      <c r="B92" s="93"/>
-    </row>
-    <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="202" t="s">
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="92"/>
+      <c r="B88" s="92"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="92"/>
+      <c r="B89" s="92"/>
+    </row>
+    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="203" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="202"/>
-      <c r="C94" s="202"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="202"/>
-      <c r="B95" s="202"/>
-      <c r="C95" s="202"/>
-    </row>
-    <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="87"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26">
+      <c r="B91" s="203"/>
+      <c r="C91" s="203"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="203"/>
+      <c r="B92" s="203"/>
+      <c r="C92" s="203"/>
+    </row>
+    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="86"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26">
         <v>40000</v>
       </c>
-      <c r="E96" s="100"/>
-    </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="87"/>
-      <c r="B97" s="89"/>
-      <c r="C97" s="86"/>
-      <c r="D97" s="100"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="32" t="s">
+      <c r="E93" s="99"/>
+    </row>
+    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="86"/>
+      <c r="B94" s="88"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="99"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="88">
-        <f>SUM(B96:B97)</f>
-        <v>0</v>
-      </c>
-      <c r="C98" s="33"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M99" s="6"/>
-    </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="201"/>
-      <c r="B100" s="201"/>
-      <c r="C100" s="201"/>
-      <c r="D100" s="201"/>
-      <c r="E100" s="201"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="201"/>
-      <c r="B101" s="201"/>
-      <c r="C101" s="201"/>
-      <c r="D101" s="201"/>
-      <c r="E101" s="201"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="201"/>
-      <c r="B102" s="201"/>
-      <c r="C102" s="201"/>
-      <c r="D102" s="201"/>
-      <c r="E102" s="201"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="201"/>
-      <c r="B103" s="201"/>
-      <c r="C103" s="201"/>
-      <c r="D103" s="201"/>
-      <c r="E103" s="201"/>
+      <c r="B95" s="87">
+        <f>SUM(B93:B94)</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="32"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M96" s="6"/>
+    </row>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="202"/>
+      <c r="B97" s="202"/>
+      <c r="C97" s="202"/>
+      <c r="D97" s="202"/>
+      <c r="E97" s="202"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="202"/>
+      <c r="B98" s="202"/>
+      <c r="C98" s="202"/>
+      <c r="D98" s="202"/>
+      <c r="E98" s="202"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="202"/>
+      <c r="B99" s="202"/>
+      <c r="C99" s="202"/>
+      <c r="D99" s="202"/>
+      <c r="E99" s="202"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="202"/>
+      <c r="B100" s="202"/>
+      <c r="C100" s="202"/>
+      <c r="D100" s="202"/>
+      <c r="E100" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2802,13 +2793,13 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A100:E103"/>
-    <mergeCell ref="A94:C95"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A97:E100"/>
+    <mergeCell ref="A91:C92"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2819,571 +2810,570 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147"/>
-      <c r="B1" s="148"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="213"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
-      <c r="M1" s="213"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="150"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="151"/>
-      <c r="B2" s="152"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154" t="s">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="138"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="141"/>
+    </row>
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="154"/>
-      <c r="G2" s="155">
-        <v>0</v>
-      </c>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154" t="s">
+      <c r="F2" s="145"/>
+      <c r="G2" s="146">
+        <v>0</v>
+      </c>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="K2" s="156">
+      <c r="K2" s="147">
         <v>2200000</v>
       </c>
-      <c r="L2" s="156"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="159"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="151"/>
-      <c r="B3" s="152"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="153"/>
-      <c r="I3" s="153"/>
-      <c r="J3" s="153"/>
-      <c r="K3" s="153"/>
-      <c r="L3" s="153"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="159"/>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="148"/>
+      <c r="N3" s="149"/>
+      <c r="O3" s="150"/>
       <c r="P3" s="20"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="222" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="224"/>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="223" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="224"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="224"/>
+      <c r="H4" s="224"/>
+      <c r="I4" s="224"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="224"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="225"/>
       <c r="P4" s="20"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="225"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="227"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="226"/>
+      <c r="B5" s="227"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="M5" s="227"/>
+      <c r="N5" s="227"/>
+      <c r="O5" s="228"/>
       <c r="P5" s="20"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="225"/>
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="226"/>
-      <c r="O6" s="227"/>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="226"/>
+      <c r="B6" s="227"/>
+      <c r="C6" s="227"/>
+      <c r="D6" s="227"/>
+      <c r="E6" s="227"/>
+      <c r="F6" s="227"/>
+      <c r="G6" s="227"/>
+      <c r="H6" s="227"/>
+      <c r="I6" s="227"/>
+      <c r="J6" s="227"/>
+      <c r="K6" s="227"/>
+      <c r="L6" s="227"/>
+      <c r="M6" s="227"/>
+      <c r="N6" s="227"/>
+      <c r="O6" s="228"/>
       <c r="P6" s="20"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="227"/>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="226"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="227"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="227"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="227"/>
+      <c r="H7" s="227"/>
+      <c r="I7" s="227"/>
+      <c r="J7" s="227"/>
+      <c r="K7" s="227"/>
+      <c r="L7" s="227"/>
+      <c r="M7" s="227"/>
+      <c r="N7" s="227"/>
+      <c r="O7" s="228"/>
       <c r="P7" s="20"/>
     </row>
-    <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="230"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="233" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="234"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="235" t="s">
+    <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="229"/>
+      <c r="B8" s="230"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="230"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="230"/>
+      <c r="H8" s="230"/>
+      <c r="I8" s="230"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="231"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="234" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="235"/>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
+      <c r="N9" s="235"/>
+      <c r="O9" s="235"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="236" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="210" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="211" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="123"/>
-      <c r="C11" s="210" t="s">
+      <c r="B11" s="117"/>
+      <c r="C11" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="210" t="s">
+      <c r="D11" s="211" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="210" t="s">
+      <c r="E11" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="214" t="s">
+      <c r="F11" s="215" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="210" t="s">
+      <c r="G11" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="218" t="s">
+      <c r="H11" s="219" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="214" t="s">
+      <c r="I11" s="215" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="214" t="s">
+      <c r="J11" s="215" t="s">
         <v>95</v>
       </c>
-      <c r="K11" s="220" t="s">
+      <c r="K11" s="221" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="214" t="s">
+      <c r="L11" s="215" t="s">
         <v>80</v>
       </c>
-      <c r="M11" s="45" t="s">
+      <c r="M11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="216" t="s">
+      <c r="N11" s="217" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="231" t="s">
+      <c r="O11" s="232" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="212"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="211"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="215"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="215"/>
-      <c r="J12" s="215"/>
-      <c r="K12" s="221"/>
-      <c r="L12" s="215"/>
-      <c r="M12" s="43" t="str">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="213"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="213"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="213"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="220"/>
+      <c r="I12" s="216"/>
+      <c r="J12" s="216"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="216"/>
+      <c r="M12" s="42" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="217"/>
-      <c r="O12" s="232"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46">
+      <c r="N12" s="218"/>
+      <c r="O12" s="233"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="45">
         <v>1</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="55">
+      <c r="D13" s="45"/>
+      <c r="E13" s="54">
         <v>12</v>
       </c>
-      <c r="F13" s="56">
-        <v>247200.01</v>
-      </c>
-      <c r="G13" s="57">
-        <f>F13-F29-F30</f>
-        <v>223199.66</v>
-      </c>
-      <c r="H13" s="58">
+      <c r="F13" s="55">
+        <v>288720.01</v>
+      </c>
+      <c r="G13" s="56">
+        <f>315120.01-F29-F30</f>
+        <v>288719.66000000003</v>
+      </c>
+      <c r="H13" s="57">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>24000.350000000006</v>
-      </c>
-      <c r="I13" s="58">
+        <v>0.34999999997671694</v>
+      </c>
+      <c r="I13" s="57">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>720.01050000000009</v>
-      </c>
-      <c r="J13" s="113">
+        <v>1.0499999999301507E-2</v>
+      </c>
+      <c r="J13" s="107">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
         <v>264000</v>
       </c>
-      <c r="K13" s="113">
+      <c r="K13" s="107">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="189">
+      <c r="L13" s="180">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="187">
+      <c r="M13" s="178">
         <f t="shared" ref="M13:M35" si="3">ROUND(SUM(H13:L13),0) + P13</f>
-        <v>288720.01</v>
-      </c>
-      <c r="N13" s="59">
+        <v>264000.01</v>
+      </c>
+      <c r="N13" s="58">
         <f>ROUND(M13*6% + M13,0) + P13</f>
-        <v>306043.01</v>
-      </c>
-      <c r="O13" s="60">
+        <v>279840.01</v>
+      </c>
+      <c r="O13" s="59">
         <f>ROUND(M13*3%,0) + M13</f>
-        <v>297382.01</v>
-      </c>
-      <c r="P13" s="31">
+        <v>271920.01</v>
+      </c>
+      <c r="P13" s="30">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="152">
         <v>2</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="47"/>
-      <c r="E14" s="55">
+      <c r="D14" s="169"/>
+      <c r="E14" s="153">
         <v>6.6</v>
       </c>
-      <c r="F14" s="56">
-        <v>143166.01999999999</v>
-      </c>
-      <c r="G14" s="57">
-        <v>148000</v>
-      </c>
-      <c r="H14" s="58">
+      <c r="F14" s="154">
+        <v>164469.01999999999</v>
+      </c>
+      <c r="G14" s="154">
+        <v>165000</v>
+      </c>
+      <c r="H14" s="155">
         <f t="shared" si="0"/>
-        <v>-4833.9800000000105</v>
-      </c>
-      <c r="I14" s="58">
+        <v>-530.98000000001048</v>
+      </c>
+      <c r="I14" s="155">
         <f t="shared" ref="I14:I35" si="4">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="113">
+      <c r="J14" s="156">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K14" s="113">
+      <c r="K14" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="189">
+      <c r="L14" s="181">
         <f>EDESUR!I6</f>
         <v>32287.37</v>
       </c>
-      <c r="M14" s="187">
+      <c r="M14" s="179">
         <f t="shared" si="3"/>
-        <v>172653.02</v>
-      </c>
-      <c r="N14" s="59">
+        <v>176956.02</v>
+      </c>
+      <c r="N14" s="157">
         <f t="shared" ref="N14:N30" si="5">ROUND(M14*6% + M14,0) + P14</f>
-        <v>183012.02</v>
-      </c>
-      <c r="O14" s="60">
+        <v>187573.02</v>
+      </c>
+      <c r="O14" s="158">
         <f t="shared" ref="O14:O35" si="6">ROUND(M14*3%,0) + M14</f>
-        <v>177833.02</v>
-      </c>
-      <c r="P14" s="31">
+        <v>182265.02</v>
+      </c>
+      <c r="P14" s="30">
         <f>P13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="46">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45">
         <v>3</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="54">
         <v>5.4</v>
       </c>
-      <c r="F15" s="56">
-        <v>108000.03</v>
-      </c>
-      <c r="G15" s="57">
+      <c r="F15" s="55">
+        <v>139551.03</v>
+      </c>
+      <c r="G15" s="56">
         <f>F15</f>
-        <v>108000.03</v>
-      </c>
-      <c r="H15" s="58">
+        <v>139551.03</v>
+      </c>
+      <c r="H15" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J15" s="113">
+      <c r="J15" s="107">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K15" s="113">
+      <c r="K15" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="189">
+      <c r="L15" s="180">
         <f>EDESUR!I7</f>
         <v>37878.74</v>
       </c>
-      <c r="M15" s="187">
+      <c r="M15" s="178">
         <f t="shared" si="3"/>
         <v>156679.03</v>
       </c>
-      <c r="N15" s="59">
+      <c r="N15" s="58">
         <f t="shared" si="5"/>
         <v>166080.03</v>
       </c>
-      <c r="O15" s="60">
+      <c r="O15" s="59">
         <f t="shared" si="6"/>
         <v>161379.03</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="30">
         <f t="shared" ref="P15:P30" si="7">P14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="45">
         <v>4</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="55">
+      <c r="D16" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="54">
         <v>6.6</v>
       </c>
-      <c r="F16" s="56">
-        <v>132000.04</v>
-      </c>
-      <c r="G16" s="57">
-        <f>144360.24-G32</f>
-        <v>132360.03999999998</v>
-      </c>
-      <c r="H16" s="58">
+      <c r="F16" s="55">
+        <v>144840.04</v>
+      </c>
+      <c r="G16" s="56">
+        <f>144840.04</f>
+        <v>144840.04</v>
+      </c>
+      <c r="H16" s="57">
         <f t="shared" si="0"/>
-        <v>-359.9999999999709</v>
-      </c>
-      <c r="I16" s="58">
+        <v>0</v>
+      </c>
+      <c r="I16" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J16" s="113">
+      <c r="J16" s="107">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K16" s="113">
+      <c r="K16" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="180">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="178">
         <f t="shared" si="3"/>
-        <v>144840.04</v>
-      </c>
-      <c r="N16" s="59">
+        <v>145200.04</v>
+      </c>
+      <c r="N16" s="58">
         <f t="shared" si="5"/>
-        <v>153530.04</v>
-      </c>
-      <c r="O16" s="60">
+        <v>153912.04</v>
+      </c>
+      <c r="O16" s="59">
         <f t="shared" si="6"/>
-        <v>149185.04</v>
-      </c>
-      <c r="P16" s="31">
+        <v>149556.04</v>
+      </c>
+      <c r="P16" s="30">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="161">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="152">
         <v>5</v>
       </c>
-      <c r="B17" s="161" t="s">
+      <c r="B17" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="161" t="s">
+      <c r="C17" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="161" t="s">
+      <c r="D17" s="152" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="162">
+      <c r="E17" s="153">
         <v>6.6</v>
       </c>
-      <c r="F17" s="163">
-        <v>132000.04999999999</v>
-      </c>
-      <c r="G17" s="163">
-        <f t="shared" ref="G17:G18" si="8">F17</f>
-        <v>132000.04999999999</v>
-      </c>
-      <c r="H17" s="164">
+      <c r="F17" s="154">
+        <v>145200.04999999999</v>
+      </c>
+      <c r="G17" s="154">
+        <v>146000</v>
+      </c>
+      <c r="H17" s="155">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="164">
+        <v>-799.95000000001164</v>
+      </c>
+      <c r="I17" s="155">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="165">
+      <c r="J17" s="156">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K17" s="165">
+      <c r="K17" s="156">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="190">
+      <c r="L17" s="181">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="188">
+      <c r="M17" s="179">
         <f t="shared" si="3"/>
-        <v>145200.04999999999</v>
-      </c>
-      <c r="N17" s="166">
+        <v>144400.04999999999</v>
+      </c>
+      <c r="N17" s="157">
         <f t="shared" si="5"/>
-        <v>153912.04999999999</v>
-      </c>
-      <c r="O17" s="167">
+        <v>153064.04999999999</v>
+      </c>
+      <c r="O17" s="158">
         <f t="shared" si="6"/>
-        <v>149556.04999999999</v>
-      </c>
-      <c r="P17" s="31">
+        <v>148732.04999999999</v>
+      </c>
+      <c r="P17" s="30">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
@@ -3391,357 +3381,359 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="45">
         <v>6</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="54">
         <v>5.4</v>
       </c>
-      <c r="F18" s="56">
-        <v>108000.06</v>
-      </c>
-      <c r="G18" s="57">
-        <f t="shared" si="8"/>
-        <v>108000.06</v>
-      </c>
-      <c r="H18" s="58">
+      <c r="F18" s="55">
+        <v>118800.06</v>
+      </c>
+      <c r="G18" s="56">
+        <f t="shared" ref="G18" si="8">F18</f>
+        <v>118800.06</v>
+      </c>
+      <c r="H18" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="58">
+      <c r="I18" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J18" s="113">
+      <c r="J18" s="107">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K18" s="113">
+      <c r="K18" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="189">
+      <c r="L18" s="180">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="187">
+      <c r="M18" s="178">
         <f t="shared" si="3"/>
         <v>118800.06</v>
       </c>
-      <c r="N18" s="59">
+      <c r="N18" s="58">
         <f t="shared" si="5"/>
         <v>125928.06</v>
       </c>
-      <c r="O18" s="60">
+      <c r="O18" s="59">
         <f t="shared" si="6"/>
         <v>122364.06</v>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="30">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="179">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="170">
         <v>7</v>
       </c>
-      <c r="B19" s="179" t="s">
+      <c r="B19" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="179" t="s">
+      <c r="C19" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="179" t="s">
+      <c r="D19" s="170" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="181">
+      <c r="E19" s="172">
         <v>5.4</v>
       </c>
-      <c r="F19" s="57">
-        <v>219240.07</v>
-      </c>
-      <c r="G19" s="57"/>
-      <c r="H19" s="182">
+      <c r="F19" s="56">
+        <v>344617.07</v>
+      </c>
+      <c r="G19" s="56">
+        <v>200000.07</v>
+      </c>
+      <c r="H19" s="173">
         <f t="shared" si="0"/>
-        <v>219240.07</v>
-      </c>
-      <c r="I19" s="182">
+        <v>144617</v>
+      </c>
+      <c r="I19" s="173">
         <f t="shared" si="4"/>
-        <v>6577.2020999999995</v>
-      </c>
-      <c r="J19" s="183">
+        <v>4338.51</v>
+      </c>
+      <c r="J19" s="174">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K19" s="183">
+      <c r="K19" s="174">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="189">
+      <c r="L19" s="180">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="187">
+      <c r="M19" s="178">
         <f t="shared" si="3"/>
-        <v>344617.07</v>
-      </c>
-      <c r="N19" s="184">
+        <v>267756.07</v>
+      </c>
+      <c r="N19" s="175">
         <f t="shared" si="5"/>
-        <v>365294.07</v>
-      </c>
-      <c r="O19" s="185">
+        <v>283821.07</v>
+      </c>
+      <c r="O19" s="176">
         <f t="shared" si="6"/>
-        <v>354956.07</v>
-      </c>
-      <c r="P19" s="31">
+        <v>275789.07</v>
+      </c>
+      <c r="P19" s="30">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="179">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="170">
         <v>8</v>
       </c>
-      <c r="B20" s="179" t="s">
+      <c r="B20" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="179" t="s">
+      <c r="C20" s="170" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="180" t="s">
+      <c r="D20" s="171" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="181">
+      <c r="E20" s="172">
         <v>6.6</v>
       </c>
-      <c r="F20" s="57">
-        <v>135960.07999999999</v>
-      </c>
-      <c r="G20" s="57">
+      <c r="F20" s="56">
+        <v>194649.09</v>
+      </c>
+      <c r="G20" s="56">
         <f>F20</f>
-        <v>135960.07999999999</v>
-      </c>
-      <c r="H20" s="182">
+        <v>194649.09</v>
+      </c>
+      <c r="H20" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="182">
+      <c r="I20" s="173">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J20" s="183">
+      <c r="J20" s="174">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K20" s="183">
+      <c r="K20" s="174">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="189">
+      <c r="L20" s="180">
         <f>EDESUR!I13</f>
         <v>93523.69</v>
       </c>
-      <c r="M20" s="187">
-        <f t="shared" si="3"/>
+      <c r="M20" s="178">
+        <f>ROUND(SUM(H20:L20),0) + P20</f>
         <v>238724.08</v>
       </c>
-      <c r="N20" s="184">
+      <c r="N20" s="175">
         <f t="shared" si="5"/>
         <v>253048.08</v>
       </c>
-      <c r="O20" s="185">
+      <c r="O20" s="176">
         <f t="shared" si="6"/>
         <v>245886.07999999999</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="30">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="46">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="45">
         <v>9</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="54">
         <v>6.6</v>
       </c>
-      <c r="F21" s="56">
-        <v>132000.09</v>
-      </c>
-      <c r="G21" s="57">
+      <c r="F21" s="55">
+        <v>145200.09</v>
+      </c>
+      <c r="G21" s="56">
         <f>F21</f>
-        <v>132000.09</v>
-      </c>
-      <c r="H21" s="58">
+        <v>145200.09</v>
+      </c>
+      <c r="H21" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J21" s="113">
+      <c r="J21" s="107">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K21" s="113">
+      <c r="K21" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="189">
+      <c r="L21" s="180">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="187">
+      <c r="M21" s="178">
         <f t="shared" si="3"/>
         <v>145200.09</v>
       </c>
-      <c r="N21" s="59">
+      <c r="N21" s="58">
         <f t="shared" si="5"/>
         <v>153912.09</v>
       </c>
-      <c r="O21" s="60">
+      <c r="O21" s="59">
         <f t="shared" si="6"/>
         <v>149556.09</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="30">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="45">
         <v>10</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="54">
         <v>5.4</v>
       </c>
-      <c r="F22" s="56">
-        <v>108000.1</v>
-      </c>
-      <c r="G22" s="57">
-        <f>F22+RESUMEN!D39+RESUMEN!D40+RESUMEN!D41</f>
-        <v>224248.22</v>
-      </c>
-      <c r="H22" s="58">
+      <c r="F22" s="55">
+        <v>2552.1</v>
+      </c>
+      <c r="G22" s="56">
+        <f>F22</f>
+        <v>2552.1</v>
+      </c>
+      <c r="H22" s="57">
         <f t="shared" si="0"/>
-        <v>-116248.12</v>
-      </c>
-      <c r="I22" s="58">
+        <v>0</v>
+      </c>
+      <c r="I22" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="113">
+      <c r="J22" s="107">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K22" s="113">
+      <c r="K22" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="189">
+      <c r="L22" s="180">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="187">
+      <c r="M22" s="178">
         <f t="shared" si="3"/>
-        <v>2552.1</v>
-      </c>
-      <c r="N22" s="59">
+        <v>118800.1</v>
+      </c>
+      <c r="N22" s="58">
         <f t="shared" si="5"/>
-        <v>2705.1</v>
-      </c>
-      <c r="O22" s="60">
+        <v>125928.1</v>
+      </c>
+      <c r="O22" s="59">
         <f t="shared" si="6"/>
-        <v>2629.1</v>
-      </c>
-      <c r="P22" s="31">
+        <v>122364.1</v>
+      </c>
+      <c r="P22" s="30">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="46">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45">
         <v>11</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="55">
+      <c r="D23" s="46"/>
+      <c r="E23" s="54">
         <v>5.4</v>
       </c>
-      <c r="F23" s="56">
-        <v>107967.11</v>
-      </c>
-      <c r="G23" s="57">
-        <f>113967.33-G34</f>
-        <v>107967.11</v>
-      </c>
-      <c r="H23" s="58">
+      <c r="F23" s="55">
+        <v>118800.11</v>
+      </c>
+      <c r="G23" s="56">
+        <f>125400-G34</f>
+        <v>118799.78</v>
+      </c>
+      <c r="H23" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="58">
+        <v>0.33000000000174623</v>
+      </c>
+      <c r="I23" s="57">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="113">
+        <v>9.900000000052386E-3</v>
+      </c>
+      <c r="J23" s="107">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K23" s="113">
+      <c r="K23" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="189">
+      <c r="L23" s="180">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="187">
+      <c r="M23" s="178">
         <f t="shared" si="3"/>
         <v>118800.11</v>
       </c>
-      <c r="N23" s="59">
+      <c r="N23" s="58">
         <f t="shared" si="5"/>
         <v>125928.11</v>
       </c>
-      <c r="O23" s="60">
+      <c r="O23" s="59">
         <f t="shared" si="6"/>
         <v>122364.11</v>
       </c>
-      <c r="P23" s="31">
+      <c r="P23" s="30">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
@@ -3749,829 +3741,829 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="46">
+    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="45">
         <v>12</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="54">
         <v>6.6</v>
       </c>
-      <c r="F24" s="56">
-        <v>132000.12</v>
-      </c>
-      <c r="G24" s="57">
-        <f>F24</f>
-        <v>132000.12</v>
-      </c>
-      <c r="H24" s="58">
+      <c r="F24" s="55">
+        <v>145200.12</v>
+      </c>
+      <c r="G24" s="56">
+        <v>132012</v>
+      </c>
+      <c r="H24" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="58">
+        <v>13188.119999999995</v>
+      </c>
+      <c r="I24" s="57">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="113">
+        <v>395.64359999999982</v>
+      </c>
+      <c r="J24" s="107">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K24" s="113">
+      <c r="K24" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="189">
+      <c r="L24" s="180">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="187">
+      <c r="M24" s="178">
         <f t="shared" si="3"/>
-        <v>145200.12</v>
-      </c>
-      <c r="N24" s="59">
+        <v>158784.12</v>
+      </c>
+      <c r="N24" s="58">
         <f t="shared" si="5"/>
-        <v>153912.12</v>
-      </c>
-      <c r="O24" s="60">
+        <v>168311.12</v>
+      </c>
+      <c r="O24" s="59">
         <f t="shared" si="6"/>
-        <v>149556.12</v>
-      </c>
-      <c r="P24" s="31">
+        <v>163548.12</v>
+      </c>
+      <c r="P24" s="30">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="46">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="45">
         <v>13</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="54">
         <v>6.6</v>
       </c>
-      <c r="F25" s="56">
-        <v>128155.13</v>
-      </c>
-      <c r="G25" s="57">
-        <v>132000.13</v>
-      </c>
-      <c r="H25" s="58">
+      <c r="F25" s="55">
+        <v>141355.13</v>
+      </c>
+      <c r="G25" s="56">
+        <v>145596.13</v>
+      </c>
+      <c r="H25" s="57">
         <f t="shared" si="0"/>
-        <v>-3845</v>
-      </c>
-      <c r="I25" s="58">
+        <v>-4241</v>
+      </c>
+      <c r="I25" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="113">
+      <c r="J25" s="107">
         <f t="shared" si="1"/>
         <v>145200</v>
       </c>
-      <c r="K25" s="113">
+      <c r="K25" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="189">
+      <c r="L25" s="180">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="187">
+      <c r="M25" s="178">
         <f t="shared" si="3"/>
-        <v>141355.13</v>
-      </c>
-      <c r="N25" s="59">
+        <v>140959.13</v>
+      </c>
+      <c r="N25" s="58">
         <f t="shared" si="5"/>
-        <v>149836.13</v>
-      </c>
-      <c r="O25" s="60">
+        <v>149417.13</v>
+      </c>
+      <c r="O25" s="59">
         <f t="shared" si="6"/>
-        <v>145596.13</v>
-      </c>
-      <c r="P25" s="31">
+        <v>145188.13</v>
+      </c>
+      <c r="P25" s="30">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="161">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="170">
         <v>14</v>
       </c>
-      <c r="B26" s="161" t="s">
+      <c r="B26" s="170" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="161" t="s">
+      <c r="C26" s="170" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="178"/>
-      <c r="E26" s="162">
+      <c r="D26" s="171"/>
+      <c r="E26" s="172">
         <v>5.4</v>
       </c>
-      <c r="F26" s="163">
-        <v>108000.14</v>
-      </c>
-      <c r="G26" s="163">
-        <v>100000</v>
-      </c>
-      <c r="H26" s="164">
+      <c r="F26" s="56">
+        <v>127040.14</v>
+      </c>
+      <c r="G26" s="56">
+        <f>F26</f>
+        <v>127040.14</v>
+      </c>
+      <c r="H26" s="173">
         <f t="shared" si="0"/>
-        <v>8000.1399999999994</v>
-      </c>
-      <c r="I26" s="164">
+        <v>0</v>
+      </c>
+      <c r="I26" s="173">
         <f t="shared" si="4"/>
-        <v>240.00419999999997</v>
-      </c>
-      <c r="J26" s="165">
+        <v>0</v>
+      </c>
+      <c r="J26" s="174">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K26" s="165">
+      <c r="K26" s="174">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="190">
+      <c r="L26" s="184">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="188">
+      <c r="M26" s="185">
         <f t="shared" si="3"/>
-        <v>127040.14</v>
-      </c>
-      <c r="N26" s="59">
+        <v>118800.14</v>
+      </c>
+      <c r="N26" s="175">
         <f t="shared" si="5"/>
-        <v>134663.14000000001</v>
-      </c>
-      <c r="O26" s="167">
+        <v>125928.14</v>
+      </c>
+      <c r="O26" s="176">
         <f t="shared" si="6"/>
-        <v>130851.14</v>
-      </c>
-      <c r="P26" s="31">
+        <v>122364.14</v>
+      </c>
+      <c r="P26" s="30">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="46">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="45">
         <v>15</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="55">
+      <c r="D27" s="46"/>
+      <c r="E27" s="54">
         <v>5.4</v>
       </c>
-      <c r="F27" s="56">
-        <v>108000.15</v>
-      </c>
-      <c r="G27" s="57">
+      <c r="F27" s="55">
+        <v>118800.15</v>
+      </c>
+      <c r="G27" s="56">
         <f t="shared" ref="G27:G35" si="9">F27</f>
-        <v>108000.15</v>
-      </c>
-      <c r="H27" s="58">
+        <v>118800.15</v>
+      </c>
+      <c r="H27" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="58">
+      <c r="I27" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="113">
+      <c r="J27" s="107">
         <f t="shared" si="1"/>
         <v>118800</v>
       </c>
-      <c r="K27" s="113">
+      <c r="K27" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="189">
+      <c r="L27" s="180">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="187">
+      <c r="M27" s="178">
         <f t="shared" si="3"/>
         <v>118800.15</v>
       </c>
-      <c r="N27" s="59">
+      <c r="N27" s="58">
         <f t="shared" si="5"/>
         <v>125928.15</v>
       </c>
-      <c r="O27" s="60">
+      <c r="O27" s="59">
         <f t="shared" si="6"/>
         <v>122364.15</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="30">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="46">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="45">
         <v>16</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="54">
         <v>0.7</v>
       </c>
-      <c r="F28" s="56">
-        <v>14000.16</v>
-      </c>
-      <c r="G28" s="57">
+      <c r="F28" s="55">
+        <v>15400.16</v>
+      </c>
+      <c r="G28" s="56">
         <f t="shared" si="9"/>
-        <v>14000.16</v>
-      </c>
-      <c r="H28" s="58">
+        <v>15400.16</v>
+      </c>
+      <c r="H28" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="58">
+      <c r="I28" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="113">
+      <c r="J28" s="107">
         <f t="shared" si="1"/>
         <v>15400</v>
       </c>
-      <c r="K28" s="113">
+      <c r="K28" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="189">
+      <c r="L28" s="180">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="M28" s="187">
+      <c r="M28" s="178">
         <f t="shared" si="3"/>
         <v>15400.16</v>
       </c>
-      <c r="N28" s="59">
+      <c r="N28" s="58">
         <f t="shared" si="5"/>
         <v>16324.16</v>
       </c>
-      <c r="O28" s="60">
+      <c r="O28" s="59">
         <f t="shared" si="6"/>
         <v>15862.16</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="30">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="46">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="45">
         <v>17</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="55">
+      <c r="D29" s="46"/>
+      <c r="E29" s="54">
         <v>0.6</v>
       </c>
-      <c r="F29" s="57">
-        <v>12000.17</v>
-      </c>
-      <c r="G29" s="57">
+      <c r="F29" s="56">
+        <v>13200.17</v>
+      </c>
+      <c r="G29" s="56">
         <f t="shared" si="9"/>
-        <v>12000.17</v>
-      </c>
-      <c r="H29" s="58">
+        <v>13200.17</v>
+      </c>
+      <c r="H29" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="58">
+      <c r="I29" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="113">
+      <c r="J29" s="107">
         <f t="shared" si="1"/>
         <v>13200</v>
       </c>
-      <c r="K29" s="113">
+      <c r="K29" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="189">
+      <c r="L29" s="180">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="M29" s="187">
+      <c r="M29" s="178">
         <f t="shared" si="3"/>
         <v>13200.17</v>
       </c>
-      <c r="N29" s="59">
+      <c r="N29" s="58">
         <f t="shared" si="5"/>
         <v>13992.17</v>
       </c>
-      <c r="O29" s="60">
+      <c r="O29" s="59">
         <f t="shared" si="6"/>
         <v>13596.17</v>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="30">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="46">
+    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="45">
         <v>18</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="91"/>
-      <c r="E30" s="55">
+      <c r="D30" s="90"/>
+      <c r="E30" s="54">
         <v>0.6</v>
       </c>
-      <c r="F30" s="56">
-        <v>12000.18</v>
-      </c>
-      <c r="G30" s="57">
+      <c r="F30" s="55">
+        <v>13200.18</v>
+      </c>
+      <c r="G30" s="56">
         <f t="shared" si="9"/>
-        <v>12000.18</v>
-      </c>
-      <c r="H30" s="58">
+        <v>13200.18</v>
+      </c>
+      <c r="H30" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="58">
+      <c r="I30" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="113">
+      <c r="J30" s="107">
         <f t="shared" si="1"/>
         <v>13200</v>
       </c>
-      <c r="K30" s="113">
+      <c r="K30" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="189">
+      <c r="L30" s="180">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="M30" s="187">
+      <c r="M30" s="178">
         <f t="shared" si="3"/>
         <v>13200.18</v>
       </c>
-      <c r="N30" s="59">
+      <c r="N30" s="58">
         <f t="shared" si="5"/>
         <v>13992.18</v>
       </c>
-      <c r="O30" s="60">
+      <c r="O30" s="59">
         <f t="shared" si="6"/>
         <v>13596.18</v>
       </c>
-      <c r="P30" s="31">
+      <c r="P30" s="30">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="179">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="170">
         <v>19</v>
       </c>
-      <c r="B31" s="179" t="s">
+      <c r="B31" s="170" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="170" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="180"/>
-      <c r="E31" s="181">
+      <c r="D31" s="171"/>
+      <c r="E31" s="172">
         <v>0.6</v>
       </c>
-      <c r="F31" s="57">
-        <v>11640.19</v>
-      </c>
-      <c r="G31" s="57">
+      <c r="F31" s="56">
+        <v>13200.19</v>
+      </c>
+      <c r="G31" s="56">
         <f t="shared" si="9"/>
-        <v>11640.19</v>
-      </c>
-      <c r="H31" s="182">
+        <v>13200.19</v>
+      </c>
+      <c r="H31" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="182">
+      <c r="I31" s="173">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="183">
+      <c r="J31" s="174">
         <f t="shared" si="1"/>
         <v>13200</v>
       </c>
-      <c r="K31" s="183">
+      <c r="K31" s="174">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="194">
+      <c r="L31" s="184">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="M31" s="195">
+      <c r="M31" s="185">
         <f t="shared" si="3"/>
         <v>13200.19</v>
       </c>
-      <c r="N31" s="184"/>
-      <c r="O31" s="185">
+      <c r="N31" s="175"/>
+      <c r="O31" s="176">
         <f t="shared" si="6"/>
         <v>13596.19</v>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="30">
         <f>P30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="61">
+    <row r="32" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="60">
         <v>20</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" s="55">
+      <c r="D32" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="54">
         <v>0.6</v>
       </c>
-      <c r="F32" s="63">
-        <v>12000.2</v>
-      </c>
-      <c r="G32" s="57">
+      <c r="F32" s="62">
+        <v>13200.2</v>
+      </c>
+      <c r="G32" s="56">
         <f t="shared" si="9"/>
-        <v>12000.2</v>
-      </c>
-      <c r="H32" s="58">
+        <v>13200.2</v>
+      </c>
+      <c r="H32" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="58">
+      <c r="I32" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J32" s="113">
+      <c r="J32" s="107">
         <f t="shared" si="1"/>
         <v>13200</v>
       </c>
-      <c r="K32" s="113">
+      <c r="K32" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="189">
+      <c r="L32" s="180">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="M32" s="187">
+      <c r="M32" s="178">
         <f t="shared" si="3"/>
         <v>13200.2</v>
       </c>
-      <c r="N32" s="59"/>
-      <c r="O32" s="60">
+      <c r="N32" s="58"/>
+      <c r="O32" s="59">
         <f t="shared" si="6"/>
         <v>13596.2</v>
       </c>
-      <c r="P32" s="31">
+      <c r="P32" s="30">
         <f t="shared" ref="P32:P35" si="10">P31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="61">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="60">
         <v>21</v>
       </c>
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="54">
         <v>0.3</v>
       </c>
-      <c r="F33" s="63">
-        <v>6000.21</v>
-      </c>
-      <c r="G33" s="57">
+      <c r="F33" s="62">
+        <v>6600.21</v>
+      </c>
+      <c r="G33" s="56">
         <f t="shared" si="9"/>
-        <v>6000.21</v>
-      </c>
-      <c r="H33" s="58">
+        <v>6600.21</v>
+      </c>
+      <c r="H33" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="58">
+      <c r="I33" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J33" s="113">
+      <c r="J33" s="107">
         <f t="shared" si="1"/>
         <v>6600</v>
       </c>
-      <c r="K33" s="113">
+      <c r="K33" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="189">
+      <c r="L33" s="180">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="M33" s="187">
+      <c r="M33" s="178">
         <f t="shared" si="3"/>
         <v>6600.21</v>
       </c>
-      <c r="N33" s="59"/>
-      <c r="O33" s="60">
+      <c r="N33" s="58"/>
+      <c r="O33" s="59">
         <f t="shared" si="6"/>
         <v>6798.21</v>
       </c>
-      <c r="P33" s="31">
+      <c r="P33" s="30">
         <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="62">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="61">
         <v>22</v>
       </c>
-      <c r="B34" s="62" t="s">
+      <c r="B34" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="55">
+      <c r="D34" s="46"/>
+      <c r="E34" s="54">
         <v>0.3</v>
       </c>
-      <c r="F34" s="63">
-        <v>6000.22</v>
-      </c>
-      <c r="G34" s="176">
+      <c r="F34" s="62">
+        <v>6600.22</v>
+      </c>
+      <c r="G34" s="167">
         <f t="shared" si="9"/>
-        <v>6000.22</v>
-      </c>
-      <c r="H34" s="58">
+        <v>6600.22</v>
+      </c>
+      <c r="H34" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="58">
+      <c r="I34" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="113">
+      <c r="J34" s="107">
         <f t="shared" si="1"/>
         <v>6600</v>
       </c>
-      <c r="K34" s="113">
+      <c r="K34" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="189">
+      <c r="L34" s="180">
         <f>EDESUR!I28</f>
         <v>0</v>
       </c>
-      <c r="M34" s="187">
+      <c r="M34" s="178">
         <f t="shared" si="3"/>
         <v>6600.22</v>
       </c>
-      <c r="N34" s="59"/>
-      <c r="O34" s="60">
+      <c r="N34" s="58"/>
+      <c r="O34" s="59">
         <f t="shared" si="6"/>
         <v>6798.22</v>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="30">
         <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="46">
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45">
         <v>23</v>
       </c>
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="54">
         <v>0.3</v>
       </c>
-      <c r="F35" s="63">
-        <v>6000.23</v>
-      </c>
-      <c r="G35" s="57">
+      <c r="F35" s="62">
+        <v>6600.23</v>
+      </c>
+      <c r="G35" s="56">
         <f t="shared" si="9"/>
-        <v>6000.23</v>
-      </c>
-      <c r="H35" s="58">
+        <v>6600.23</v>
+      </c>
+      <c r="H35" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="113">
+      <c r="J35" s="107">
         <f t="shared" si="1"/>
         <v>6600</v>
       </c>
-      <c r="K35" s="113">
+      <c r="K35" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="189">
+      <c r="L35" s="180">
         <f>EDESUR!I29</f>
         <v>0</v>
       </c>
-      <c r="M35" s="187">
+      <c r="M35" s="178">
         <f t="shared" si="3"/>
         <v>6600.23</v>
       </c>
-      <c r="N35" s="65"/>
-      <c r="O35" s="60">
+      <c r="N35" s="64"/>
+      <c r="O35" s="59">
         <f t="shared" si="6"/>
         <v>6798.23</v>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="30">
         <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="66"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="125">
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="65"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="119">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="39">
         <f>SUM(F13:F35)</f>
-        <v>2129330.7600000007</v>
-      </c>
-      <c r="G36" s="44">
+        <v>2427795.7700000009</v>
+      </c>
+      <c r="G36" s="43">
         <f>SUM(G13:G35)</f>
-        <v>2003377.2999999993</v>
-      </c>
-      <c r="H36" s="44">
+        <v>2275561.9000000008</v>
+      </c>
+      <c r="H36" s="43">
         <f>SUM(H13:H35)</f>
-        <v>125953.46000000004</v>
-      </c>
-      <c r="I36" s="44">
+        <v>152233.86999999994</v>
+      </c>
+      <c r="I36" s="43">
         <f t="shared" ref="I36:N36" si="11">SUM(I13:I35)</f>
-        <v>7537.2168000000001</v>
-      </c>
-      <c r="J36" s="94">
+        <v>4734.1739999999991</v>
+      </c>
+      <c r="J36" s="93">
         <f t="shared" si="11"/>
         <v>2200000</v>
       </c>
-      <c r="K36" s="44">
+      <c r="K36" s="43">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L36" s="186"/>
-      <c r="M36" s="68">
+      <c r="L36" s="177"/>
+      <c r="M36" s="67">
         <f>SUM(M13:M35)</f>
-        <v>2497182.7600000012</v>
-      </c>
-      <c r="N36" s="68">
+        <v>2520660.7600000012</v>
+      </c>
+      <c r="N36" s="67">
         <f t="shared" si="11"/>
-        <v>2598040.7100000009</v>
-      </c>
-      <c r="O36" s="68">
+        <v>2622927.7100000009</v>
+      </c>
+      <c r="O36" s="67">
         <f>SUM(O13:O35)</f>
-        <v>2572099.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-    </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="201" t="str">
+        <v>2596281.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+    </row>
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="202" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="201"/>
-      <c r="E39" s="201"/>
-      <c r="F39" s="201"/>
-      <c r="G39" s="201"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="201"/>
-      <c r="J39" s="201"/>
-      <c r="K39" s="201"/>
-      <c r="L39" s="201"/>
-      <c r="M39" s="201"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="201"/>
-      <c r="D40" s="201"/>
-      <c r="E40" s="201"/>
-      <c r="F40" s="201"/>
-      <c r="G40" s="201"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="201"/>
-      <c r="J40" s="201"/>
-      <c r="K40" s="201"/>
-      <c r="L40" s="201"/>
-      <c r="M40" s="201"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="201"/>
-      <c r="D41" s="201"/>
-      <c r="E41" s="201"/>
-      <c r="F41" s="201"/>
-      <c r="G41" s="201"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="201"/>
-      <c r="J41" s="201"/>
-      <c r="K41" s="201"/>
-      <c r="L41" s="201"/>
-      <c r="M41" s="201"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="201"/>
-      <c r="D42" s="201"/>
-      <c r="E42" s="201"/>
-      <c r="F42" s="201"/>
-      <c r="G42" s="201"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="201"/>
-      <c r="J42" s="201"/>
-      <c r="K42" s="201"/>
-      <c r="L42" s="201"/>
-      <c r="M42" s="201"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="201"/>
-      <c r="D43" s="201"/>
-      <c r="E43" s="201"/>
-      <c r="F43" s="201"/>
-      <c r="G43" s="201"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="201"/>
-      <c r="J43" s="201"/>
-      <c r="K43" s="201"/>
-      <c r="L43" s="201"/>
-      <c r="M43" s="201"/>
-    </row>
-    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="201"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
-      <c r="F44" s="201"/>
-      <c r="G44" s="201"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="201"/>
-      <c r="J44" s="201"/>
-      <c r="K44" s="201"/>
-      <c r="L44" s="201"/>
-      <c r="M44" s="201"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+      <c r="G39" s="202"/>
+      <c r="H39" s="202"/>
+      <c r="I39" s="202"/>
+      <c r="J39" s="202"/>
+      <c r="K39" s="202"/>
+      <c r="L39" s="202"/>
+      <c r="M39" s="202"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+      <c r="G40" s="202"/>
+      <c r="H40" s="202"/>
+      <c r="I40" s="202"/>
+      <c r="J40" s="202"/>
+      <c r="K40" s="202"/>
+      <c r="L40" s="202"/>
+      <c r="M40" s="202"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="202"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="202"/>
+      <c r="I41" s="202"/>
+      <c r="J41" s="202"/>
+      <c r="K41" s="202"/>
+      <c r="L41" s="202"/>
+      <c r="M41" s="202"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="202"/>
+      <c r="F42" s="202"/>
+      <c r="G42" s="202"/>
+      <c r="H42" s="202"/>
+      <c r="I42" s="202"/>
+      <c r="J42" s="202"/>
+      <c r="K42" s="202"/>
+      <c r="L42" s="202"/>
+      <c r="M42" s="202"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="202"/>
+      <c r="I43" s="202"/>
+      <c r="J43" s="202"/>
+      <c r="K43" s="202"/>
+      <c r="L43" s="202"/>
+      <c r="M43" s="202"/>
+    </row>
+    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="202"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="202"/>
+      <c r="F44" s="202"/>
+      <c r="G44" s="202"/>
+      <c r="H44" s="202"/>
+      <c r="I44" s="202"/>
+      <c r="J44" s="202"/>
+      <c r="K44" s="202"/>
+      <c r="L44" s="202"/>
+      <c r="M44" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4602,589 +4594,589 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="134" t="s">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="125" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="134" t="s">
+      <c r="C3" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="136" t="s">
+      <c r="E3" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="175" t="s">
+      <c r="G3" s="166" t="s">
         <v>122</v>
       </c>
-      <c r="I3" s="238" t="s">
+      <c r="I3" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="239"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="G4" s="137"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="239"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="134">
+      <c r="J3" s="240"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="G4" s="128"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="240"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="125">
         <v>1</v>
       </c>
-      <c r="C5" s="134" t="s">
+      <c r="C5" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="138">
+      <c r="E5" s="129">
         <v>4778.67</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="139">
+      <c r="G5" s="130">
         <f>E5</f>
         <v>4778.67</v>
       </c>
-      <c r="I5" s="236">
+      <c r="I5" s="237">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="237"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="134">
+      <c r="J5" s="238"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="125">
         <v>1</v>
       </c>
-      <c r="C6" s="134" t="s">
+      <c r="C6" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="138">
+      <c r="E6" s="129">
         <v>32287.37</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="139">
-        <v>0</v>
-      </c>
-      <c r="I6" s="236">
-        <f t="shared" ref="I6:I21" si="0">E6-G6</f>
+      <c r="G6" s="130">
+        <v>0</v>
+      </c>
+      <c r="I6" s="237">
+        <f t="shared" ref="I6:I19" si="0">E6-G6</f>
         <v>32287.37</v>
       </c>
-      <c r="J6" s="237"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="134">
+      <c r="J6" s="238"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="125">
         <v>1</v>
       </c>
-      <c r="C7" s="134" t="s">
+      <c r="C7" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="138">
+      <c r="E7" s="129">
         <v>37878.74</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="139"/>
-      <c r="I7" s="236">
+      <c r="G7" s="130"/>
+      <c r="I7" s="237">
         <f t="shared" si="0"/>
         <v>37878.74</v>
       </c>
-      <c r="J7" s="237"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="134">
+      <c r="J7" s="238"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="125">
         <v>2</v>
       </c>
-      <c r="C8" s="134" t="s">
+      <c r="C8" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="138">
+      <c r="E8" s="129">
         <v>2150.4</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="139">
+      <c r="G8" s="130">
         <f>E8</f>
         <v>2150.4</v>
       </c>
-      <c r="I8" s="236">
+      <c r="I8" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="237"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="135">
+      <c r="J8" s="238"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="126">
         <v>2</v>
       </c>
-      <c r="C9" s="135" t="s">
+      <c r="C9" s="126" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="138">
+      <c r="E9" s="129">
         <v>2628.27</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="139">
+      <c r="G9" s="130">
         <f>E9</f>
         <v>2628.27</v>
       </c>
-      <c r="I9" s="236">
+      <c r="I9" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="237"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="135">
+      <c r="J9" s="238"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="126">
         <v>2</v>
       </c>
-      <c r="C10" s="135" t="s">
+      <c r="C10" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="138">
+      <c r="E10" s="129">
         <v>2628.27</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="139">
+      <c r="G10" s="130">
         <f>E10</f>
         <v>2628.27</v>
       </c>
-      <c r="I10" s="236">
+      <c r="I10" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="237"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="135">
+      <c r="J10" s="238"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="126">
         <v>2</v>
       </c>
-      <c r="C11" s="135" t="s">
+      <c r="C11" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="138">
+      <c r="E11" s="129">
         <v>2150.4</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="139">
+      <c r="G11" s="130">
         <f>E11</f>
         <v>2150.4</v>
       </c>
-      <c r="I11" s="236">
+      <c r="I11" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="237"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="135">
+      <c r="J11" s="238"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="126">
         <v>3</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="138">
+      <c r="E12" s="129">
         <v>2150.4</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="139">
+      <c r="G12" s="130">
         <f>E12</f>
         <v>2150.4</v>
       </c>
-      <c r="I12" s="236">
+      <c r="I12" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="237"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="134">
+      <c r="J12" s="238"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="125">
         <v>3</v>
       </c>
-      <c r="C13" s="134" t="s">
+      <c r="C13" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="138">
+      <c r="E13" s="129">
         <v>93523.69</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="139"/>
-      <c r="I13" s="236">
+      <c r="G13" s="130"/>
+      <c r="I13" s="237">
         <f t="shared" si="0"/>
         <v>93523.69</v>
       </c>
-      <c r="J13" s="237"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="135">
+      <c r="J13" s="238"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="126">
         <v>3</v>
       </c>
-      <c r="C14" s="135" t="s">
+      <c r="C14" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="129">
         <v>2628.27</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="139">
-        <f>E14</f>
+      <c r="G14" s="130">
+        <f t="shared" ref="G14:G19" si="1">E14</f>
         <v>2628.27</v>
       </c>
-      <c r="I14" s="236">
+      <c r="I14" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="237"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="135">
+      <c r="J14" s="238"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="126">
         <v>3</v>
       </c>
-      <c r="C15" s="135" t="s">
+      <c r="C15" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="138">
+      <c r="E15" s="129">
         <v>2150.4</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="139">
-        <f>E15</f>
+      <c r="G15" s="130">
+        <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I15" s="236">
+      <c r="I15" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="237"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="134">
+      <c r="J15" s="238"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="125">
         <v>4</v>
       </c>
-      <c r="C16" s="134" t="s">
+      <c r="C16" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="138">
+      <c r="E16" s="129">
         <v>2150.4</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="139">
-        <f>E16</f>
+      <c r="G16" s="130">
+        <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I16" s="236">
+      <c r="I16" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="237"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="135">
+      <c r="J16" s="238"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="126">
         <v>4</v>
       </c>
-      <c r="C17" s="135" t="s">
+      <c r="C17" s="126" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="138">
+      <c r="E17" s="129">
         <v>2628.27</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="139">
-        <f>E17</f>
+      <c r="G17" s="130">
+        <f t="shared" si="1"/>
         <v>2628.27</v>
       </c>
-      <c r="I17" s="236">
+      <c r="I17" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="237"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="134">
+      <c r="J17" s="238"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="125">
         <v>4</v>
       </c>
-      <c r="C18" s="134" t="s">
+      <c r="C18" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="138">
+      <c r="E18" s="129">
         <v>2628.27</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="139">
-        <f>E18</f>
+      <c r="G18" s="130">
+        <f t="shared" si="1"/>
         <v>2628.27</v>
       </c>
-      <c r="I18" s="236">
+      <c r="I18" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="237"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="135">
+      <c r="J18" s="238"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="126">
         <v>4</v>
       </c>
-      <c r="C19" s="135" t="s">
+      <c r="C19" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="138">
+      <c r="E19" s="129">
         <v>2150.4</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="139">
-        <f>E19</f>
+      <c r="G19" s="130">
+        <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I19" s="236">
+      <c r="I19" s="237">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="237"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="134"/>
-      <c r="C20" s="134"/>
-      <c r="E20" s="134"/>
-      <c r="G20" s="137"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="237"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="168" t="s">
+      <c r="J19" s="238"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="G20" s="128"/>
+      <c r="I20" s="237"/>
+      <c r="J20" s="238"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="159" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="168"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="170">
+      <c r="C21" s="159"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="161">
         <f>SUM(E5:E20)</f>
         <v>194512.21999999994</v>
       </c>
-      <c r="F21" s="171"/>
-      <c r="G21" s="170">
+      <c r="F21" s="162"/>
+      <c r="G21" s="161">
         <f>SUM(G5:G20)</f>
         <v>30822.420000000006</v>
       </c>
-      <c r="I21" s="236">
+      <c r="I21" s="237">
         <f>E21-G21</f>
         <v>163689.79999999993</v>
       </c>
-      <c r="J21" s="237"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="134" t="s">
+      <c r="J21" s="238"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="134">
+      <c r="C22" s="125">
         <v>1</v>
       </c>
-      <c r="E22" s="144">
+      <c r="E22" s="135">
         <v>278.76</v>
       </c>
-      <c r="G22" s="145">
+      <c r="G22" s="136">
         <f>E22</f>
         <v>278.76</v>
       </c>
-      <c r="I22" s="236">
-        <f t="shared" ref="I22" si="1">E22-G22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="237"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="134" t="s">
+      <c r="I22" s="237">
+        <f t="shared" ref="I22" si="2">E22-G22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="238"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="134">
+      <c r="C23" s="125">
         <v>2</v>
       </c>
-      <c r="E23" s="144">
+      <c r="E23" s="135">
         <v>238.93</v>
       </c>
-      <c r="G23" s="145">
-        <f t="shared" ref="G23:G29" si="2">E23</f>
+      <c r="G23" s="136">
+        <f t="shared" ref="G23:G29" si="3">E23</f>
         <v>238.93</v>
       </c>
-      <c r="I23" s="236">
-        <f t="shared" ref="I23:I31" si="3">E23-G23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="237"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="134" t="s">
+      <c r="I23" s="237">
+        <f t="shared" ref="I23:I31" si="4">E23-G23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="238"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="134">
+      <c r="C24" s="125">
         <v>3</v>
       </c>
-      <c r="E24" s="144">
+      <c r="E24" s="135">
         <v>238.93</v>
       </c>
-      <c r="G24" s="145">
-        <f t="shared" si="2"/>
+      <c r="G24" s="136">
+        <f t="shared" si="3"/>
         <v>238.93</v>
       </c>
-      <c r="I24" s="236">
+      <c r="I24" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="238"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="125" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="125">
+        <v>4</v>
+      </c>
+      <c r="E25" s="135">
+        <v>238.93</v>
+      </c>
+      <c r="G25" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="237"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="134" t="s">
+        <v>238.93</v>
+      </c>
+      <c r="I25" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="238"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="134">
-        <v>4</v>
-      </c>
-      <c r="E25" s="144">
+      <c r="C26" s="125">
+        <v>5</v>
+      </c>
+      <c r="E26" s="135">
         <v>238.93</v>
       </c>
-      <c r="G25" s="145">
-        <f t="shared" si="2"/>
+      <c r="G26" s="136">
+        <f t="shared" si="3"/>
         <v>238.93</v>
       </c>
-      <c r="I25" s="236">
+      <c r="I26" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="238"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="125" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="125">
+        <v>6</v>
+      </c>
+      <c r="E27" s="135">
+        <v>119.47</v>
+      </c>
+      <c r="G27" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="237"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="134" t="s">
+        <v>119.47</v>
+      </c>
+      <c r="I27" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="238"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="134">
-        <v>5</v>
-      </c>
-      <c r="E26" s="144">
-        <v>238.93</v>
-      </c>
-      <c r="G26" s="145">
-        <f t="shared" si="2"/>
-        <v>238.93</v>
-      </c>
-      <c r="I26" s="236">
+      <c r="C28" s="125">
+        <v>7</v>
+      </c>
+      <c r="E28" s="135">
+        <v>119.47</v>
+      </c>
+      <c r="G28" s="136">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="237"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="134" t="s">
+        <v>119.47</v>
+      </c>
+      <c r="I28" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="238"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="134">
-        <v>6</v>
-      </c>
-      <c r="E27" s="144">
+      <c r="C29" s="125">
+        <v>8</v>
+      </c>
+      <c r="E29" s="135">
         <v>119.47</v>
       </c>
-      <c r="G27" s="145">
-        <f t="shared" si="2"/>
+      <c r="G29" s="136">
+        <f t="shared" si="3"/>
         <v>119.47</v>
       </c>
-      <c r="I27" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="237"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="134">
-        <v>7</v>
-      </c>
-      <c r="E28" s="144">
-        <v>119.47</v>
-      </c>
-      <c r="G28" s="145">
-        <f t="shared" si="2"/>
-        <v>119.47</v>
-      </c>
-      <c r="I28" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="237"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="134">
-        <v>8</v>
-      </c>
-      <c r="E29" s="144">
-        <v>119.47</v>
-      </c>
-      <c r="G29" s="145">
-        <f t="shared" si="2"/>
-        <v>119.47</v>
-      </c>
-      <c r="I29" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="237"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="173" t="s">
+      <c r="I29" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="238"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="164" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="174"/>
-      <c r="D30" s="172"/>
-      <c r="E30" s="170">
+      <c r="C30" s="165"/>
+      <c r="D30" s="163"/>
+      <c r="E30" s="161">
         <f>SUM(E22:E29)</f>
         <v>1592.8900000000003</v>
       </c>
-      <c r="F30" s="172"/>
-      <c r="G30" s="170">
+      <c r="F30" s="163"/>
+      <c r="G30" s="161">
         <f>SUM(G22:G29)</f>
         <v>1592.8900000000003</v>
       </c>
-      <c r="I30" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="237"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="142"/>
-      <c r="G31" s="139"/>
-      <c r="I31" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="237"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="140"/>
-      <c r="G32" s="141"/>
-      <c r="I32" s="236"/>
-      <c r="J32" s="237"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="142">
+      <c r="I30" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="238"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="133"/>
+      <c r="G31" s="130"/>
+      <c r="I31" s="237">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="238"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="131"/>
+      <c r="G32" s="132"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="238"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="133">
         <f>E30+E21</f>
         <v>196105.10999999996</v>
       </c>
-      <c r="G33" s="139">
+      <c r="G33" s="130">
         <f>G21+G30</f>
         <v>32415.310000000005</v>
       </c>
-      <c r="I33" s="236">
+      <c r="I33" s="237">
         <f>E33-G33</f>
         <v>163689.79999999996</v>
       </c>
-      <c r="J33" s="237"/>
+      <c r="J33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
+++ b/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747566AE-820F-4B08-81FD-394621C17F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4511C10-4716-4429-8CFA-C6AC74D22AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1447,12 +1447,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1462,101 +1480,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2003,12 +2003,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="204" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="208"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -2046,49 +2046,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="210" t="s">
+      <c r="B8" s="207" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="210"/>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="210"/>
-      <c r="C9" s="210"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="209" t="s">
+      <c r="A13" s="206" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="209"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2114,10 +2114,10 @@
       <c r="E21" s="100"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="200" t="s">
+      <c r="A22" s="202" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="201"/>
+      <c r="B22" s="203"/>
       <c r="C22" s="38"/>
       <c r="D22" s="110">
         <v>473045</v>
@@ -2128,8 +2128,8 @@
       <c r="H22" s="89"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="200"/>
-      <c r="B23" s="201"/>
+      <c r="A23" s="202"/>
+      <c r="B23" s="203"/>
       <c r="C23" s="38"/>
       <c r="D23" s="110"/>
       <c r="E23" s="103"/>
@@ -2157,10 +2157,10 @@
       <c r="E25" s="190"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="200" t="s">
+      <c r="A26" s="202" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="201"/>
+      <c r="B26" s="203"/>
       <c r="C26" s="40"/>
       <c r="D26" s="168">
         <v>75267</v>
@@ -2227,10 +2227,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="205" t="s">
+      <c r="A32" s="200" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="206"/>
+      <c r="B32" s="201"/>
       <c r="C32" s="5"/>
       <c r="D32" s="104">
         <v>174848.74</v>
@@ -2272,10 +2272,10 @@
       <c r="E35" s="193"/>
     </row>
     <row r="36" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="200" t="s">
+      <c r="A36" s="202" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="201"/>
+      <c r="B36" s="203"/>
       <c r="C36" s="5"/>
       <c r="D36" s="104">
         <v>75000</v>
@@ -2311,10 +2311,10 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="200" t="s">
+      <c r="A39" s="202" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="201"/>
+      <c r="B39" s="203"/>
       <c r="C39" s="5"/>
       <c r="D39" s="74">
         <v>157988.29</v>
@@ -2322,10 +2322,10 @@
       <c r="E39" s="105"/>
     </row>
     <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="200" t="s">
+      <c r="A40" s="202" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="201"/>
+      <c r="B40" s="203"/>
       <c r="C40" s="5"/>
       <c r="D40" s="74">
         <v>50000</v>
@@ -2356,10 +2356,10 @@
       <c r="E42" s="194"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="200" t="s">
+      <c r="A43" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="201"/>
+      <c r="B43" s="203"/>
       <c r="C43" s="38"/>
       <c r="D43" s="110" t="s">
         <v>138</v>
@@ -2494,8 +2494,8 @@
       <c r="E57" s="72"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="204"/>
-      <c r="B58" s="204"/>
+      <c r="A58" s="210"/>
+      <c r="B58" s="210"/>
       <c r="C58" s="5"/>
       <c r="D58" s="104"/>
       <c r="E58" s="72"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B77" s="97">
         <f>PRORRATEO!G36-B85</f>
-        <v>2275561.9000000008</v>
+        <v>2433550.1900000009</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B80" s="95">
         <f>SUM(B74:C79)</f>
-        <v>419847.65999999992</v>
+        <v>577835.94999999995</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -2718,16 +2718,16 @@
     </row>
     <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="203" t="s">
+      <c r="A91" s="209" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="203"/>
-      <c r="C91" s="203"/>
+      <c r="B91" s="209"/>
+      <c r="C91" s="209"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="203"/>
-      <c r="B92" s="203"/>
-      <c r="C92" s="203"/>
+      <c r="A92" s="209"/>
+      <c r="B92" s="209"/>
+      <c r="C92" s="209"/>
     </row>
     <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="86"/>
@@ -2757,35 +2757,42 @@
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="202"/>
-      <c r="B97" s="202"/>
-      <c r="C97" s="202"/>
-      <c r="D97" s="202"/>
-      <c r="E97" s="202"/>
+      <c r="A97" s="208"/>
+      <c r="B97" s="208"/>
+      <c r="C97" s="208"/>
+      <c r="D97" s="208"/>
+      <c r="E97" s="208"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="202"/>
-      <c r="B98" s="202"/>
-      <c r="C98" s="202"/>
-      <c r="D98" s="202"/>
-      <c r="E98" s="202"/>
+      <c r="A98" s="208"/>
+      <c r="B98" s="208"/>
+      <c r="C98" s="208"/>
+      <c r="D98" s="208"/>
+      <c r="E98" s="208"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="202"/>
-      <c r="B99" s="202"/>
-      <c r="C99" s="202"/>
-      <c r="D99" s="202"/>
-      <c r="E99" s="202"/>
+      <c r="A99" s="208"/>
+      <c r="B99" s="208"/>
+      <c r="C99" s="208"/>
+      <c r="D99" s="208"/>
+      <c r="E99" s="208"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="202"/>
-      <c r="B100" s="202"/>
-      <c r="C100" s="202"/>
-      <c r="D100" s="202"/>
-      <c r="E100" s="202"/>
+      <c r="A100" s="208"/>
+      <c r="B100" s="208"/>
+      <c r="C100" s="208"/>
+      <c r="D100" s="208"/>
+      <c r="E100" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A97:E100"/>
+    <mergeCell ref="A91:C92"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2793,13 +2800,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A97:E100"/>
-    <mergeCell ref="A91:C92"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2835,15 +2835,15 @@
       <c r="B1" s="139"/>
       <c r="C1" s="140"/>
       <c r="D1" s="140"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
       <c r="N1" s="139"/>
       <c r="O1" s="141"/>
     </row>
@@ -2892,198 +2892,198 @@
       <c r="P3" s="20"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="222" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="224"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="225"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="224"/>
       <c r="P4" s="20"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="226"/>
-      <c r="B5" s="227"/>
-      <c r="C5" s="227"/>
-      <c r="D5" s="227"/>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="227"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="227"/>
-      <c r="N5" s="227"/>
-      <c r="O5" s="228"/>
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="227"/>
       <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="226"/>
-      <c r="B6" s="227"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="227"/>
-      <c r="E6" s="227"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="227"/>
-      <c r="H6" s="227"/>
-      <c r="I6" s="227"/>
-      <c r="J6" s="227"/>
-      <c r="K6" s="227"/>
-      <c r="L6" s="227"/>
-      <c r="M6" s="227"/>
-      <c r="N6" s="227"/>
-      <c r="O6" s="228"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="227"/>
       <c r="P6" s="20"/>
     </row>
     <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="226"/>
-      <c r="B7" s="227"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="227"/>
-      <c r="E7" s="227"/>
-      <c r="F7" s="227"/>
-      <c r="G7" s="227"/>
-      <c r="H7" s="227"/>
-      <c r="I7" s="227"/>
-      <c r="J7" s="227"/>
-      <c r="K7" s="227"/>
-      <c r="L7" s="227"/>
-      <c r="M7" s="227"/>
-      <c r="N7" s="227"/>
-      <c r="O7" s="228"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="227"/>
       <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="229"/>
-      <c r="B8" s="230"/>
-      <c r="C8" s="230"/>
-      <c r="D8" s="230"/>
-      <c r="E8" s="230"/>
-      <c r="F8" s="230"/>
-      <c r="G8" s="230"/>
-      <c r="H8" s="230"/>
-      <c r="I8" s="230"/>
-      <c r="J8" s="230"/>
-      <c r="K8" s="230"/>
-      <c r="L8" s="230"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="230"/>
-      <c r="O8" s="231"/>
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="230"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="233" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="236" t="s">
+      <c r="A10" s="235" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
+      <c r="B10" s="235"/>
+      <c r="C10" s="235"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
+      <c r="N10" s="235"/>
+      <c r="O10" s="235"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="211" t="s">
+      <c r="A11" s="216" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="117"/>
-      <c r="C11" s="211" t="s">
+      <c r="C11" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="211" t="s">
+      <c r="D11" s="216" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="211" t="s">
+      <c r="E11" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="215" t="s">
+      <c r="F11" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="211" t="s">
+      <c r="G11" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="219" t="s">
+      <c r="H11" s="218" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="215" t="s">
+      <c r="I11" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="215" t="s">
+      <c r="J11" s="212" t="s">
         <v>95</v>
       </c>
-      <c r="K11" s="221" t="s">
+      <c r="K11" s="220" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="215" t="s">
+      <c r="L11" s="212" t="s">
         <v>80</v>
       </c>
       <c r="M11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="217" t="s">
+      <c r="N11" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="232" t="s">
+      <c r="O11" s="231" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="213"/>
+      <c r="A12" s="217"/>
       <c r="B12" s="118"/>
-      <c r="C12" s="213"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="216"/>
-      <c r="G12" s="213"/>
-      <c r="H12" s="220"/>
-      <c r="I12" s="216"/>
-      <c r="J12" s="216"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="216"/>
+      <c r="C12" s="217"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="213"/>
+      <c r="K12" s="221"/>
+      <c r="L12" s="213"/>
       <c r="M12" s="42" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="218"/>
-      <c r="O12" s="233"/>
+      <c r="N12" s="215"/>
+      <c r="O12" s="232"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45">
@@ -3640,12 +3640,12 @@
         <v>2552.1</v>
       </c>
       <c r="G22" s="56">
-        <f>F22</f>
-        <v>2552.1</v>
+        <f>F22+RESUMEN!D39</f>
+        <v>160540.39000000001</v>
       </c>
       <c r="H22" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-157988.29</v>
       </c>
       <c r="I22" s="57">
         <f t="shared" si="4"/>
@@ -3665,15 +3665,15 @@
       </c>
       <c r="M22" s="178">
         <f t="shared" si="3"/>
-        <v>118800.1</v>
+        <v>-39187.9</v>
       </c>
       <c r="N22" s="58">
         <f t="shared" si="5"/>
-        <v>125928.1</v>
+        <v>-41538.9</v>
       </c>
       <c r="O22" s="59">
         <f t="shared" si="6"/>
-        <v>122364.1</v>
+        <v>-40363.9</v>
       </c>
       <c r="P22" s="30">
         <f t="shared" si="7"/>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="G36" s="43">
         <f>SUM(G13:G35)</f>
-        <v>2275561.9000000008</v>
+        <v>2433550.1900000009</v>
       </c>
       <c r="H36" s="43">
         <f>SUM(H13:H35)</f>
-        <v>152233.86999999994</v>
+        <v>-5754.4200000000565</v>
       </c>
       <c r="I36" s="43">
         <f t="shared" ref="I36:N36" si="11">SUM(I13:I35)</f>
@@ -4468,15 +4468,15 @@
       <c r="L36" s="177"/>
       <c r="M36" s="67">
         <f>SUM(M13:M35)</f>
-        <v>2520660.7600000012</v>
+        <v>2362672.7600000012</v>
       </c>
       <c r="N36" s="67">
         <f t="shared" si="11"/>
-        <v>2622927.7100000009</v>
+        <v>2455460.7100000009</v>
       </c>
       <c r="O36" s="67">
         <f>SUM(O13:O35)</f>
-        <v>2596281.7600000012</v>
+        <v>2433553.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4485,88 +4485,93 @@
     </row>
     <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="202" t="str">
+      <c r="C39" s="208" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="202"/>
-      <c r="E39" s="202"/>
-      <c r="F39" s="202"/>
-      <c r="G39" s="202"/>
-      <c r="H39" s="202"/>
-      <c r="I39" s="202"/>
-      <c r="J39" s="202"/>
-      <c r="K39" s="202"/>
-      <c r="L39" s="202"/>
-      <c r="M39" s="202"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="208"/>
+      <c r="H39" s="208"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="208"/>
     </row>
     <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="202"/>
-      <c r="D40" s="202"/>
-      <c r="E40" s="202"/>
-      <c r="F40" s="202"/>
-      <c r="G40" s="202"/>
-      <c r="H40" s="202"/>
-      <c r="I40" s="202"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="202"/>
+      <c r="C40" s="208"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
     </row>
     <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="202"/>
-      <c r="D41" s="202"/>
-      <c r="E41" s="202"/>
-      <c r="F41" s="202"/>
-      <c r="G41" s="202"/>
-      <c r="H41" s="202"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="202"/>
-      <c r="K41" s="202"/>
-      <c r="L41" s="202"/>
-      <c r="M41" s="202"/>
+      <c r="C41" s="208"/>
+      <c r="D41" s="208"/>
+      <c r="E41" s="208"/>
+      <c r="F41" s="208"/>
+      <c r="G41" s="208"/>
+      <c r="H41" s="208"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="208"/>
     </row>
     <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="202"/>
-      <c r="D42" s="202"/>
-      <c r="E42" s="202"/>
-      <c r="F42" s="202"/>
-      <c r="G42" s="202"/>
-      <c r="H42" s="202"/>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="202"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="202"/>
+      <c r="C42" s="208"/>
+      <c r="D42" s="208"/>
+      <c r="E42" s="208"/>
+      <c r="F42" s="208"/>
+      <c r="G42" s="208"/>
+      <c r="H42" s="208"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="208"/>
     </row>
     <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="202"/>
-      <c r="D43" s="202"/>
-      <c r="E43" s="202"/>
-      <c r="F43" s="202"/>
-      <c r="G43" s="202"/>
-      <c r="H43" s="202"/>
-      <c r="I43" s="202"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="202"/>
-      <c r="L43" s="202"/>
-      <c r="M43" s="202"/>
+      <c r="C43" s="208"/>
+      <c r="D43" s="208"/>
+      <c r="E43" s="208"/>
+      <c r="F43" s="208"/>
+      <c r="G43" s="208"/>
+      <c r="H43" s="208"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="208"/>
     </row>
     <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="202"/>
-      <c r="D44" s="202"/>
-      <c r="E44" s="202"/>
-      <c r="F44" s="202"/>
-      <c r="G44" s="202"/>
-      <c r="H44" s="202"/>
-      <c r="I44" s="202"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="202"/>
-      <c r="L44" s="202"/>
-      <c r="M44" s="202"/>
+      <c r="C44" s="208"/>
+      <c r="D44" s="208"/>
+      <c r="E44" s="208"/>
+      <c r="F44" s="208"/>
+      <c r="G44" s="208"/>
+      <c r="H44" s="208"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4580,11 +4585,6 @@
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A10:O10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:M44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -5180,6 +5180,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5196,21 +5211,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
+++ b/2026/SALTA 1167/Marzo/SALTA1167-Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4511C10-4716-4429-8CFA-C6AC74D22AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB239E9-FA68-4369-9D99-3A7065AD19B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1116,7 +1111,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1410,7 +1405,6 @@
     <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1423,12 +1417,6 @@
     <xf numFmtId="44" fontId="17" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1447,18 +1435,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1471,14 +1462,14 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1495,12 +1486,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1554,9 +1539,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1648,9 +1630,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1688,9 +1670,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1723,26 +1705,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1775,26 +1740,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1969,21 +1917,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="50" t="s">
         <v>75</v>
@@ -1992,7 +1940,7 @@
       <c r="D1" s="50"/>
       <c r="E1" s="51"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="52" t="s">
         <v>14</v>
@@ -2001,16 +1949,16 @@
       <c r="D2" s="52"/>
       <c r="E2" s="53"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="205"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="203"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2021,7 +1969,7 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>76</v>
       </c>
@@ -2034,7 +1982,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>130</v>
       </c>
@@ -2045,57 +1993,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="207" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="207"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="C8" s="205"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="204" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="206"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>105</v>
       </c>
@@ -2104,7 +2052,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>78</v>
       </c>
@@ -2113,11 +2061,11 @@
       <c r="D21" s="109"/>
       <c r="E21" s="100"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="195" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="203"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="38"/>
       <c r="D22" s="110">
         <v>473045</v>
@@ -2127,49 +2075,49 @@
       </c>
       <c r="H22" s="89"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
-      <c r="B23" s="203"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="195"/>
+      <c r="B23" s="196"/>
       <c r="C23" s="38"/>
       <c r="D23" s="110"/>
       <c r="E23" s="103"/>
       <c r="H23" s="89"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
       <c r="D24" s="111"/>
-      <c r="E24" s="189">
+      <c r="E24" s="186">
         <f>SUM(D22:D23)</f>
         <v>473045</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="112"/>
-      <c r="E25" s="190"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202" t="s">
+      <c r="E25" s="187"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="203"/>
+      <c r="B26" s="196"/>
       <c r="C26" s="40"/>
       <c r="D26" s="168">
         <v>75267</v>
       </c>
-      <c r="E26" s="186" t="s">
+      <c r="E26" s="185" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
@@ -2181,16 +2129,16 @@
         <v>75267</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="101"/>
       <c r="C28" s="101"/>
       <c r="D28" s="113"/>
-      <c r="E28" s="191"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="188"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
@@ -2199,7 +2147,7 @@
       <c r="D29" s="104"/>
       <c r="E29" s="103"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>67</v>
       </c>
@@ -2213,7 +2161,7 @@
         <v>Transf 04/03</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>67</v>
       </c>
@@ -2226,7 +2174,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="200" t="s">
         <v>69</v>
       </c>
@@ -2239,7 +2187,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="106" t="s">
         <v>79</v>
       </c>
@@ -2252,30 +2200,30 @@
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="114"/>
-      <c r="E34" s="192">
+      <c r="E34" s="189">
         <f>SUM(D29:D33)</f>
         <v>451330.93999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="111"/>
-      <c r="E35" s="193"/>
-    </row>
-    <row r="36" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="202" t="s">
+      <c r="E35" s="190"/>
+    </row>
+    <row r="36" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="195" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="203"/>
+      <c r="B36" s="196"/>
       <c r="C36" s="5"/>
       <c r="D36" s="104">
         <v>75000</v>
@@ -2284,11 +2232,11 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="187" t="s">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="121" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="188"/>
+      <c r="B37" s="122"/>
       <c r="C37" s="5"/>
       <c r="D37" s="74">
         <v>4800</v>
@@ -2297,11 +2245,11 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="198" t="s">
+    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="121" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="199"/>
+      <c r="B38" s="122"/>
       <c r="C38" s="5"/>
       <c r="D38" s="74">
         <v>60000</v>
@@ -2310,22 +2258,22 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="202" t="s">
+    <row r="39" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="195" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="203"/>
+      <c r="B39" s="196"/>
       <c r="C39" s="5"/>
       <c r="D39" s="74">
         <v>157988.29</v>
       </c>
       <c r="E39" s="105"/>
     </row>
-    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="202" t="s">
+    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="195" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="203"/>
+      <c r="B40" s="196"/>
       <c r="C40" s="5"/>
       <c r="D40" s="74">
         <v>50000</v>
@@ -2334,7 +2282,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>6</v>
       </c>
@@ -2346,49 +2294,49 @@
         <v>347788.29000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>11</v>
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
       <c r="D42" s="109"/>
-      <c r="E42" s="194"/>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="202" t="s">
+      <c r="E42" s="191"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="203"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="38"/>
       <c r="D43" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="195"/>
+      <c r="E43" s="192"/>
       <c r="G43" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="121"/>
       <c r="B44" s="122"/>
       <c r="C44" s="38"/>
       <c r="D44" s="134"/>
-      <c r="E44" s="195"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E44" s="192"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="111"/>
-      <c r="E45" s="189">
+      <c r="E45" s="186">
         <f>SUM(D43:D44)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>8</v>
       </c>
@@ -2397,16 +2345,16 @@
       <c r="D46" s="108"/>
       <c r="E46" s="123"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="104"/>
-      <c r="E47" s="196"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E47" s="193"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>117</v>
       </c>
@@ -2415,9 +2363,9 @@
       <c r="D48" s="104">
         <v>27165.99</v>
       </c>
-      <c r="E48" s="197"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E48" s="194"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>9</v>
       </c>
@@ -2429,14 +2377,14 @@
         <v>27165.99</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="71"/>
       <c r="E50" s="77"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>101</v>
       </c>
@@ -2448,13 +2396,13 @@
         <v>825402.78</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="D52" s="79"/>
       <c r="E52" s="80"/>
       <c r="F52" s="30"/>
     </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>97</v>
       </c>
@@ -2468,16 +2416,16 @@
       <c r="F53" s="99"/>
       <c r="G53" s="30"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D54" s="79"/>
       <c r="E54" s="79"/>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D55" s="79"/>
       <c r="E55" s="79"/>
       <c r="H55" s="115"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>98</v>
       </c>
@@ -2486,35 +2434,35 @@
       <c r="D56" s="83"/>
       <c r="E56" s="84"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="73"/>
       <c r="B57" s="102"/>
       <c r="C57" s="5"/>
       <c r="D57" s="74"/>
       <c r="E57" s="72"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="210"/>
-      <c r="B58" s="210"/>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="199"/>
+      <c r="B58" s="199"/>
       <c r="C58" s="5"/>
       <c r="D58" s="104"/>
       <c r="E58" s="72"/>
     </row>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="73"/>
       <c r="B60" s="75"/>
       <c r="C60" s="5"/>
       <c r="D60" s="74"/>
       <c r="E60" s="72"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="35"/>
       <c r="B61" s="34"/>
       <c r="C61" s="34"/>
@@ -2524,19 +2472,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>100</v>
       </c>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
       <c r="D64" s="23"/>
-      <c r="E64" s="182"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E64" s="181"/>
+    </row>
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>99</v>
       </c>
@@ -2548,8 +2496,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="69" t="s">
         <v>106</v>
       </c>
@@ -2558,7 +2506,7 @@
         <v>2200000</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="69" t="s">
         <v>107</v>
       </c>
@@ -2567,7 +2515,7 @@
         <v>1374597.22</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="69" t="s">
         <v>108</v>
       </c>
@@ -2576,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="69" t="s">
         <v>109</v>
       </c>
@@ -2585,12 +2533,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73"/>
       <c r="B73" s="29"/>
       <c r="C73" s="27"/>
     </row>
-    <row r="74" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="91" t="s">
         <v>110</v>
       </c>
@@ -2600,7 +2548,7 @@
       <c r="C74" s="27"/>
       <c r="D74" s="33"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="40" t="s">
         <v>103</v>
       </c>
@@ -2609,7 +2557,7 @@
         <v>-1374597.22</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
         <v>25</v>
       </c>
@@ -2618,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="40" t="s">
         <v>112</v>
       </c>
@@ -2627,19 +2575,19 @@
         <v>2433550.1900000009</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="40" t="s">
         <v>124</v>
       </c>
       <c r="B78" s="97"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="98" t="s">
         <v>24</v>
       </c>
       <c r="B79" s="116"/>
     </row>
-    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="94" t="s">
         <v>114</v>
       </c>
@@ -2648,13 +2596,13 @@
         <v>577835.94999999995</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="92"/>
       <c r="B81" s="92"/>
       <c r="D81" s="30"/>
       <c r="E81" s="29"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="91" t="s">
         <v>111</v>
       </c>
@@ -2664,7 +2612,7 @@
       <c r="D82" s="29"/>
       <c r="E82" s="30"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="40" t="s">
         <v>104</v>
       </c>
@@ -2674,7 +2622,7 @@
       </c>
       <c r="D83" s="30"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="40" t="s">
         <v>25</v>
       </c>
@@ -2684,22 +2632,22 @@
       </c>
       <c r="D84" s="30"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="40" t="s">
         <v>113</v>
       </c>
       <c r="B85" s="97">
         <v>0</v>
       </c>
-      <c r="D85" s="183"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D85" s="182"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="98" t="s">
         <v>24</v>
       </c>
       <c r="B86" s="116"/>
     </row>
-    <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="94" t="s">
         <v>115</v>
       </c>
@@ -2708,28 +2656,28 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="92"/>
       <c r="B88" s="92"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="92"/>
       <c r="B89" s="92"/>
     </row>
-    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="209" t="s">
+    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="198" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="209"/>
-      <c r="C91" s="209"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="209"/>
-      <c r="B92" s="209"/>
-      <c r="C92" s="209"/>
-    </row>
-    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="198"/>
+      <c r="C91" s="198"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="198"/>
+      <c r="B92" s="198"/>
+      <c r="C92" s="198"/>
+    </row>
+    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="86"/>
       <c r="B93" s="26"/>
       <c r="C93" s="26">
@@ -2737,13 +2685,13 @@
       </c>
       <c r="E93" s="99"/>
     </row>
-    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="86"/>
       <c r="B94" s="88"/>
       <c r="C94" s="85"/>
       <c r="D94" s="99"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="31" t="s">
         <v>6</v>
       </c>
@@ -2753,39 +2701,46 @@
       </c>
       <c r="C95" s="32"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="208"/>
-      <c r="B97" s="208"/>
-      <c r="C97" s="208"/>
-      <c r="D97" s="208"/>
-      <c r="E97" s="208"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="208"/>
-      <c r="B98" s="208"/>
-      <c r="C98" s="208"/>
-      <c r="D98" s="208"/>
-      <c r="E98" s="208"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="208"/>
-      <c r="B99" s="208"/>
-      <c r="C99" s="208"/>
-      <c r="D99" s="208"/>
-      <c r="E99" s="208"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="208"/>
-      <c r="B100" s="208"/>
-      <c r="C100" s="208"/>
-      <c r="D100" s="208"/>
-      <c r="E100" s="208"/>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="197"/>
+      <c r="B97" s="197"/>
+      <c r="C97" s="197"/>
+      <c r="D97" s="197"/>
+      <c r="E97" s="197"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="197"/>
+      <c r="B98" s="197"/>
+      <c r="C98" s="197"/>
+      <c r="D98" s="197"/>
+      <c r="E98" s="197"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="197"/>
+      <c r="B99" s="197"/>
+      <c r="C99" s="197"/>
+      <c r="D99" s="197"/>
+      <c r="E99" s="197"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="197"/>
+      <c r="B100" s="197"/>
+      <c r="C100" s="197"/>
+      <c r="D100" s="197"/>
+      <c r="E100" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A97:E100"/>
     <mergeCell ref="A91:C92"/>
@@ -2793,13 +2748,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2810,44 +2758,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5546875" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="138"/>
       <c r="B1" s="139"/>
       <c r="C1" s="140"/>
       <c r="D1" s="140"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="209"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
       <c r="N1" s="139"/>
       <c r="O1" s="141"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="142"/>
       <c r="B2" s="143"/>
       <c r="C2" s="144"/>
@@ -2873,7 +2821,7 @@
       <c r="O2" s="150"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="142"/>
       <c r="B3" s="143"/>
       <c r="C3" s="144"/>
@@ -2891,201 +2839,201 @@
       <c r="O3" s="150"/>
       <c r="P3" s="20"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="222" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="218" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="224"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="219"/>
+      <c r="E4" s="219"/>
+      <c r="F4" s="219"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="219"/>
+      <c r="I4" s="219"/>
+      <c r="J4" s="219"/>
+      <c r="K4" s="219"/>
+      <c r="L4" s="219"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="220"/>
       <c r="P4" s="20"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="225"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="227"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="223"/>
       <c r="P5" s="20"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="225"/>
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="226"/>
-      <c r="O6" s="227"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="221"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="222"/>
+      <c r="N6" s="222"/>
+      <c r="O6" s="223"/>
       <c r="P6" s="20"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="227"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
+      <c r="M7" s="222"/>
+      <c r="N7" s="222"/>
+      <c r="O7" s="223"/>
       <c r="P7" s="20"/>
     </row>
-    <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="230"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="233" t="s">
+    <row r="8" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="224"/>
+      <c r="B8" s="225"/>
+      <c r="C8" s="225"/>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="226"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="229" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="234"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="235" t="s">
+      <c r="B9" s="230"/>
+      <c r="C9" s="230"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="230"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="230"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="230"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="230"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="230"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="230"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="231" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="216" t="s">
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="231"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="231"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="231"/>
+      <c r="O10" s="231"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="206" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="117"/>
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="216" t="s">
+      <c r="D11" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="216" t="s">
+      <c r="E11" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="212" t="s">
+      <c r="F11" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="216" t="s">
+      <c r="G11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="218" t="s">
+      <c r="H11" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="212" t="s">
+      <c r="I11" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="212" t="s">
+      <c r="J11" s="210" t="s">
         <v>95</v>
       </c>
-      <c r="K11" s="220" t="s">
+      <c r="K11" s="216" t="s">
         <v>96</v>
       </c>
-      <c r="L11" s="212" t="s">
+      <c r="L11" s="210" t="s">
         <v>80</v>
       </c>
       <c r="M11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="214" t="s">
+      <c r="N11" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="231" t="s">
+      <c r="O11" s="227" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="217"/>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="208"/>
       <c r="B12" s="118"/>
-      <c r="C12" s="217"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="217"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="217"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="213"/>
-      <c r="K12" s="221"/>
-      <c r="L12" s="213"/>
+      <c r="C12" s="208"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="208"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="215"/>
+      <c r="I12" s="211"/>
+      <c r="J12" s="211"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="211"/>
       <c r="M12" s="42" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="215"/>
-      <c r="O12" s="232"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="213"/>
+      <c r="O12" s="228"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45">
         <v>1</v>
       </c>
@@ -3122,11 +3070,11 @@
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="180">
+      <c r="L13" s="179">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="178">
+      <c r="M13" s="177">
         <f t="shared" ref="M13:M35" si="3">ROUND(SUM(H13:L13),0) + P13</f>
         <v>264000.01</v>
       </c>
@@ -3142,7 +3090,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="152">
         <v>2</v>
       </c>
@@ -3178,11 +3126,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="181">
+      <c r="L14" s="180">
         <f>EDESUR!I6</f>
         <v>32287.37</v>
       </c>
-      <c r="M14" s="179">
+      <c r="M14" s="178">
         <f t="shared" si="3"/>
         <v>176956.02</v>
       </c>
@@ -3199,7 +3147,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="45">
         <v>3</v>
       </c>
@@ -3238,11 +3186,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="179">
         <f>EDESUR!I7</f>
         <v>37878.74</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="177">
         <f t="shared" si="3"/>
         <v>156679.03</v>
       </c>
@@ -3259,7 +3207,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45">
         <v>4</v>
       </c>
@@ -3298,11 +3246,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="180">
+      <c r="L16" s="179">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="178">
+      <c r="M16" s="177">
         <f t="shared" si="3"/>
         <v>145200.04</v>
       </c>
@@ -3319,7 +3267,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="152">
         <v>5</v>
       </c>
@@ -3357,11 +3305,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="181">
+      <c r="L17" s="180">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="179">
+      <c r="M17" s="178">
         <f t="shared" si="3"/>
         <v>144400.04999999999</v>
       </c>
@@ -3381,7 +3329,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45">
         <v>6</v>
       </c>
@@ -3420,11 +3368,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="180">
+      <c r="L18" s="179">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="178">
+      <c r="M18" s="177">
         <f t="shared" si="3"/>
         <v>118800.06</v>
       </c>
@@ -3441,7 +3389,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="170">
         <v>7</v>
       </c>
@@ -3479,11 +3427,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="180">
+      <c r="L19" s="179">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="178">
+      <c r="M19" s="177">
         <f t="shared" si="3"/>
         <v>267756.07</v>
       </c>
@@ -3500,7 +3448,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="170">
         <v>8</v>
       </c>
@@ -3539,11 +3487,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="180">
+      <c r="L20" s="179">
         <f>EDESUR!I13</f>
         <v>93523.69</v>
       </c>
-      <c r="M20" s="178">
+      <c r="M20" s="177">
         <f>ROUND(SUM(H20:L20),0) + P20</f>
         <v>238724.08</v>
       </c>
@@ -3560,7 +3508,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45">
         <v>9</v>
       </c>
@@ -3580,12 +3528,12 @@
         <v>145200.09</v>
       </c>
       <c r="G21" s="56">
-        <f>F21</f>
-        <v>145200.09</v>
+        <f>F21+39187.9</f>
+        <v>184387.99</v>
       </c>
       <c r="H21" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-39187.899999999994</v>
       </c>
       <c r="I21" s="57">
         <f t="shared" si="4"/>
@@ -3599,28 +3547,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="180">
+      <c r="L21" s="179">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="178">
+      <c r="M21" s="177">
         <f t="shared" si="3"/>
-        <v>145200.09</v>
+        <v>106012.09</v>
       </c>
       <c r="N21" s="58">
         <f t="shared" si="5"/>
-        <v>153912.09</v>
+        <v>112373.09</v>
       </c>
       <c r="O21" s="59">
         <f t="shared" si="6"/>
-        <v>149556.09</v>
+        <v>109192.09</v>
       </c>
       <c r="P21" s="30">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45">
         <v>10</v>
       </c>
@@ -3640,12 +3588,12 @@
         <v>2552.1</v>
       </c>
       <c r="G22" s="56">
-        <f>F22+RESUMEN!D39</f>
-        <v>160540.39000000001</v>
+        <f>F22+RESUMEN!D39-39187.9</f>
+        <v>121352.49000000002</v>
       </c>
       <c r="H22" s="57">
-        <f t="shared" si="0"/>
-        <v>-157988.29</v>
+        <f>F22-G22</f>
+        <v>-118800.39000000001</v>
       </c>
       <c r="I22" s="57">
         <f t="shared" si="4"/>
@@ -3659,28 +3607,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="180">
+      <c r="L22" s="179">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="178">
+      <c r="M22" s="177">
         <f t="shared" si="3"/>
-        <v>-39187.9</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="N22" s="58">
         <f t="shared" si="5"/>
-        <v>-41538.9</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="O22" s="59">
         <f t="shared" si="6"/>
-        <v>-40363.9</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="P22" s="30">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>11</v>
       </c>
@@ -3717,11 +3665,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="180">
+      <c r="L23" s="179">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="178">
+      <c r="M23" s="177">
         <f t="shared" si="3"/>
         <v>118800.11</v>
       </c>
@@ -3741,7 +3689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45">
         <v>12</v>
       </c>
@@ -3779,11 +3727,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="180">
+      <c r="L24" s="179">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="178">
+      <c r="M24" s="177">
         <f t="shared" si="3"/>
         <v>158784.12</v>
       </c>
@@ -3800,7 +3748,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45">
         <v>13</v>
       </c>
@@ -3838,11 +3786,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="180">
+      <c r="L25" s="179">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="178">
+      <c r="M25" s="177">
         <f t="shared" si="3"/>
         <v>140959.13</v>
       </c>
@@ -3859,7 +3807,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="170">
         <v>14</v>
       </c>
@@ -3896,11 +3844,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="184">
+      <c r="L26" s="183">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="185">
+      <c r="M26" s="184">
         <f t="shared" si="3"/>
         <v>118800.14</v>
       </c>
@@ -3917,7 +3865,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>15</v>
       </c>
@@ -3954,11 +3902,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="180">
+      <c r="L27" s="179">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="178">
+      <c r="M27" s="177">
         <f t="shared" si="3"/>
         <v>118800.15</v>
       </c>
@@ -3975,7 +3923,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>16</v>
       </c>
@@ -4014,11 +3962,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="180">
+      <c r="L28" s="179">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="M28" s="178">
+      <c r="M28" s="177">
         <f t="shared" si="3"/>
         <v>15400.16</v>
       </c>
@@ -4035,7 +3983,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>17</v>
       </c>
@@ -4072,11 +4020,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="180">
+      <c r="L29" s="179">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="M29" s="178">
+      <c r="M29" s="177">
         <f t="shared" si="3"/>
         <v>13200.17</v>
       </c>
@@ -4093,7 +4041,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>18</v>
       </c>
@@ -4130,11 +4078,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="180">
+      <c r="L30" s="179">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="M30" s="178">
+      <c r="M30" s="177">
         <f t="shared" si="3"/>
         <v>13200.18</v>
       </c>
@@ -4151,7 +4099,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="170">
         <v>19</v>
       </c>
@@ -4188,11 +4136,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="184">
+      <c r="L31" s="183">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="M31" s="185">
+      <c r="M31" s="184">
         <f t="shared" si="3"/>
         <v>13200.19</v>
       </c>
@@ -4206,7 +4154,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A32" s="60">
         <v>20</v>
       </c>
@@ -4245,11 +4193,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="180">
+      <c r="L32" s="179">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="M32" s="178">
+      <c r="M32" s="177">
         <f t="shared" si="3"/>
         <v>13200.2</v>
       </c>
@@ -4263,7 +4211,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="60">
         <v>21</v>
       </c>
@@ -4302,11 +4250,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="180">
+      <c r="L33" s="179">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="M33" s="178">
+      <c r="M33" s="177">
         <f t="shared" si="3"/>
         <v>6600.21</v>
       </c>
@@ -4320,7 +4268,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="61">
         <v>22</v>
       </c>
@@ -4357,11 +4305,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="180">
+      <c r="L34" s="179">
         <f>EDESUR!I28</f>
         <v>0</v>
       </c>
-      <c r="M34" s="178">
+      <c r="M34" s="177">
         <f t="shared" si="3"/>
         <v>6600.22</v>
       </c>
@@ -4375,7 +4323,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="45">
         <v>23</v>
       </c>
@@ -4414,11 +4362,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="180">
+      <c r="L35" s="179">
         <f>EDESUR!I29</f>
         <v>0</v>
       </c>
-      <c r="M35" s="178">
+      <c r="M35" s="177">
         <f t="shared" si="3"/>
         <v>6600.23</v>
       </c>
@@ -4432,7 +4380,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="65"/>
       <c r="B36" s="65"/>
       <c r="C36" s="66"/>
@@ -4465,7 +4413,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L36" s="177"/>
+      <c r="L36" s="67">
+        <f>SUM(L13:L35)</f>
+        <v>163689.79999999999</v>
+      </c>
       <c r="M36" s="67">
         <f>SUM(M13:M35)</f>
         <v>2362672.7600000012</v>
@@ -4479,99 +4430,94 @@
         <v>2433553.7600000012</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="36"/>
       <c r="D37" s="36"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="208" t="str">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="208"/>
-      <c r="E39" s="208"/>
-      <c r="F39" s="208"/>
-      <c r="G39" s="208"/>
-      <c r="H39" s="208"/>
-      <c r="I39" s="208"/>
-      <c r="J39" s="208"/>
-      <c r="K39" s="208"/>
-      <c r="L39" s="208"/>
-      <c r="M39" s="208"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="208"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="208"/>
-      <c r="D41" s="208"/>
-      <c r="E41" s="208"/>
-      <c r="F41" s="208"/>
-      <c r="G41" s="208"/>
-      <c r="H41" s="208"/>
-      <c r="I41" s="208"/>
-      <c r="J41" s="208"/>
-      <c r="K41" s="208"/>
-      <c r="L41" s="208"/>
-      <c r="M41" s="208"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="208"/>
-      <c r="D42" s="208"/>
-      <c r="E42" s="208"/>
-      <c r="F42" s="208"/>
-      <c r="G42" s="208"/>
-      <c r="H42" s="208"/>
-      <c r="I42" s="208"/>
-      <c r="J42" s="208"/>
-      <c r="K42" s="208"/>
-      <c r="L42" s="208"/>
-      <c r="M42" s="208"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="208"/>
-      <c r="D43" s="208"/>
-      <c r="E43" s="208"/>
-      <c r="F43" s="208"/>
-      <c r="G43" s="208"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="208"/>
-      <c r="K43" s="208"/>
-      <c r="L43" s="208"/>
-      <c r="M43" s="208"/>
-    </row>
-    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="208"/>
-      <c r="D44" s="208"/>
-      <c r="E44" s="208"/>
-      <c r="F44" s="208"/>
-      <c r="G44" s="208"/>
-      <c r="H44" s="208"/>
-      <c r="I44" s="208"/>
-      <c r="J44" s="208"/>
-      <c r="K44" s="208"/>
-      <c r="L44" s="208"/>
-      <c r="M44" s="208"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="197"/>
+      <c r="J39" s="197"/>
+      <c r="K39" s="197"/>
+      <c r="L39" s="197"/>
+      <c r="M39" s="197"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="197"/>
+      <c r="J40" s="197"/>
+      <c r="K40" s="197"/>
+      <c r="L40" s="197"/>
+      <c r="M40" s="197"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="197"/>
+      <c r="D41" s="197"/>
+      <c r="E41" s="197"/>
+      <c r="F41" s="197"/>
+      <c r="G41" s="197"/>
+      <c r="H41" s="197"/>
+      <c r="I41" s="197"/>
+      <c r="J41" s="197"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="197"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="197"/>
+      <c r="D42" s="197"/>
+      <c r="E42" s="197"/>
+      <c r="F42" s="197"/>
+      <c r="G42" s="197"/>
+      <c r="H42" s="197"/>
+      <c r="I42" s="197"/>
+      <c r="J42" s="197"/>
+      <c r="K42" s="197"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="197"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="197"/>
+      <c r="D43" s="197"/>
+      <c r="E43" s="197"/>
+      <c r="F43" s="197"/>
+      <c r="G43" s="197"/>
+      <c r="H43" s="197"/>
+      <c r="I43" s="197"/>
+      <c r="J43" s="197"/>
+      <c r="K43" s="197"/>
+      <c r="L43" s="197"/>
+      <c r="M43" s="197"/>
+    </row>
+    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="197"/>
+      <c r="D44" s="197"/>
+      <c r="E44" s="197"/>
+      <c r="F44" s="197"/>
+      <c r="G44" s="197"/>
+      <c r="H44" s="197"/>
+      <c r="I44" s="197"/>
+      <c r="J44" s="197"/>
+      <c r="K44" s="197"/>
+      <c r="L44" s="197"/>
+      <c r="M44" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C39:M44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4585,6 +4531,11 @@
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A10:O10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4594,17 +4545,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="125" t="s">
         <v>81</v>
       </c>
@@ -4617,20 +4568,20 @@
       <c r="G3" s="166" t="s">
         <v>122</v>
       </c>
-      <c r="I3" s="239" t="s">
+      <c r="I3" s="234" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="240"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="235"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="125"/>
       <c r="C4" s="125"/>
       <c r="E4" s="125"/>
       <c r="G4" s="128"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="240"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="234"/>
+      <c r="J4" s="235"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="125">
         <v>1</v>
       </c>
@@ -4645,13 +4596,13 @@
         <f>E5</f>
         <v>4778.67</v>
       </c>
-      <c r="I5" s="237">
+      <c r="I5" s="232">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="238"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="233"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="125">
         <v>1</v>
       </c>
@@ -4665,13 +4616,13 @@
       <c r="G6" s="130">
         <v>0</v>
       </c>
-      <c r="I6" s="237">
+      <c r="I6" s="232">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
         <v>32287.37</v>
       </c>
-      <c r="J6" s="238"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="233"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="125">
         <v>1</v>
       </c>
@@ -4683,13 +4634,13 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="130"/>
-      <c r="I7" s="237">
+      <c r="I7" s="232">
         <f t="shared" si="0"/>
         <v>37878.74</v>
       </c>
-      <c r="J7" s="238"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="233"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="125">
         <v>2</v>
       </c>
@@ -4704,13 +4655,13 @@
         <f>E8</f>
         <v>2150.4</v>
       </c>
-      <c r="I8" s="237">
+      <c r="I8" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="238"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="233"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="126">
         <v>2</v>
       </c>
@@ -4725,13 +4676,13 @@
         <f>E9</f>
         <v>2628.27</v>
       </c>
-      <c r="I9" s="237">
+      <c r="I9" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="238"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="233"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="126">
         <v>2</v>
       </c>
@@ -4746,13 +4697,13 @@
         <f>E10</f>
         <v>2628.27</v>
       </c>
-      <c r="I10" s="237">
+      <c r="I10" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="238"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="233"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="126">
         <v>2</v>
       </c>
@@ -4767,13 +4718,13 @@
         <f>E11</f>
         <v>2150.4</v>
       </c>
-      <c r="I11" s="237">
+      <c r="I11" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="238"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="233"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="126">
         <v>3</v>
       </c>
@@ -4788,13 +4739,13 @@
         <f>E12</f>
         <v>2150.4</v>
       </c>
-      <c r="I12" s="237">
+      <c r="I12" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="238"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="233"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="125">
         <v>3</v>
       </c>
@@ -4806,13 +4757,13 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="130"/>
-      <c r="I13" s="237">
+      <c r="I13" s="232">
         <f t="shared" si="0"/>
         <v>93523.69</v>
       </c>
-      <c r="J13" s="238"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="233"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="126">
         <v>3</v>
       </c>
@@ -4827,13 +4778,13 @@
         <f t="shared" ref="G14:G19" si="1">E14</f>
         <v>2628.27</v>
       </c>
-      <c r="I14" s="237">
+      <c r="I14" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="238"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="233"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="126">
         <v>3</v>
       </c>
@@ -4848,13 +4799,13 @@
         <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I15" s="237">
+      <c r="I15" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="238"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="233"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="125">
         <v>4</v>
       </c>
@@ -4869,13 +4820,13 @@
         <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I16" s="237">
+      <c r="I16" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="238"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="233"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="126">
         <v>4</v>
       </c>
@@ -4890,13 +4841,13 @@
         <f t="shared" si="1"/>
         <v>2628.27</v>
       </c>
-      <c r="I17" s="237">
+      <c r="I17" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="238"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="233"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="125">
         <v>4</v>
       </c>
@@ -4911,13 +4862,13 @@
         <f t="shared" si="1"/>
         <v>2628.27</v>
       </c>
-      <c r="I18" s="237">
+      <c r="I18" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="238"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="233"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="126">
         <v>4</v>
       </c>
@@ -4932,21 +4883,21 @@
         <f t="shared" si="1"/>
         <v>2150.4</v>
       </c>
-      <c r="I19" s="237">
+      <c r="I19" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="238"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="233"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="125"/>
       <c r="C20" s="125"/>
       <c r="E20" s="125"/>
       <c r="G20" s="128"/>
-      <c r="I20" s="237"/>
-      <c r="J20" s="238"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I20" s="232"/>
+      <c r="J20" s="233"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="159" t="s">
         <v>121</v>
       </c>
@@ -4961,13 +4912,13 @@
         <f>SUM(G5:G20)</f>
         <v>30822.420000000006</v>
       </c>
-      <c r="I21" s="237">
+      <c r="I21" s="232">
         <f>E21-G21</f>
         <v>163689.79999999993</v>
       </c>
-      <c r="J21" s="238"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="233"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="125" t="s">
         <v>87</v>
       </c>
@@ -4981,13 +4932,13 @@
         <f>E22</f>
         <v>278.76</v>
       </c>
-      <c r="I22" s="237">
+      <c r="I22" s="232">
         <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="238"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="233"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="125" t="s">
         <v>87</v>
       </c>
@@ -5001,13 +4952,13 @@
         <f t="shared" ref="G23:G29" si="3">E23</f>
         <v>238.93</v>
       </c>
-      <c r="I23" s="237">
+      <c r="I23" s="232">
         <f t="shared" ref="I23:I31" si="4">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="238"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="233"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="125" t="s">
         <v>87</v>
       </c>
@@ -5021,13 +4972,13 @@
         <f t="shared" si="3"/>
         <v>238.93</v>
       </c>
-      <c r="I24" s="237">
+      <c r="I24" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="238"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="233"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="125" t="s">
         <v>87</v>
       </c>
@@ -5041,13 +4992,13 @@
         <f t="shared" si="3"/>
         <v>238.93</v>
       </c>
-      <c r="I25" s="237">
+      <c r="I25" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="238"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="233"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="125" t="s">
         <v>87</v>
       </c>
@@ -5061,13 +5012,13 @@
         <f t="shared" si="3"/>
         <v>238.93</v>
       </c>
-      <c r="I26" s="237">
+      <c r="I26" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="238"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="233"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="125" t="s">
         <v>87</v>
       </c>
@@ -5081,13 +5032,13 @@
         <f t="shared" si="3"/>
         <v>119.47</v>
       </c>
-      <c r="I27" s="237">
+      <c r="I27" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="238"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="233"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="125" t="s">
         <v>87</v>
       </c>
@@ -5101,13 +5052,13 @@
         <f t="shared" si="3"/>
         <v>119.47</v>
       </c>
-      <c r="I28" s="237">
+      <c r="I28" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="238"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="233"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="125" t="s">
         <v>87</v>
       </c>
@@ -5121,13 +5072,13 @@
         <f t="shared" si="3"/>
         <v>119.47</v>
       </c>
-      <c r="I29" s="237">
+      <c r="I29" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="238"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="233"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="164" t="s">
         <v>121</v>
       </c>
@@ -5142,28 +5093,28 @@
         <f>SUM(G22:G29)</f>
         <v>1592.8900000000003</v>
       </c>
-      <c r="I30" s="237">
+      <c r="I30" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="238"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="233"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="133"/>
       <c r="G31" s="130"/>
-      <c r="I31" s="237">
+      <c r="I31" s="232">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="238"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="233"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="131"/>
       <c r="G32" s="132"/>
-      <c r="I32" s="237"/>
-      <c r="J32" s="238"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="232"/>
+      <c r="J32" s="233"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="133">
         <f>E30+E21</f>
         <v>196105.10999999996</v>
@@ -5172,29 +5123,14 @@
         <f>G21+G30</f>
         <v>32415.310000000005</v>
       </c>
-      <c r="I33" s="237">
+      <c r="I33" s="232">
         <f>E33-G33</f>
         <v>163689.79999999996</v>
       </c>
-      <c r="J33" s="238"/>
+      <c r="J33" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5211,6 +5147,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
